--- a/data-raw/workbooks/kelpbio-6-refit-nereo.xlsx
+++ b/data-raw/workbooks/kelpbio-6-refit-nereo.xlsx
@@ -396,10 +396,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
-        <v>38.7</v>
+        <v>57.5</v>
       </c>
       <c r="B2">
-        <v>0.379</v>
+        <v>4.268</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -410,10 +410,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
-        <v>13.1</v>
+        <v>31.5</v>
       </c>
       <c r="B3">
-        <v>0.021</v>
+        <v>0.78</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -424,10 +424,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
-        <v>33.4</v>
+        <v>19.7</v>
       </c>
       <c r="B4">
-        <v>0.181</v>
+        <v>0.097</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -438,10 +438,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="B5">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C5" t="s">
         <v>4</v>
@@ -452,10 +452,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
-        <v>29.7</v>
+        <v>19.3</v>
       </c>
       <c r="B6">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -466,10 +466,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
-        <v>33.3</v>
+        <v>34.2</v>
       </c>
       <c r="B7">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
@@ -480,10 +480,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
-        <v>36.1</v>
+        <v>53.9</v>
       </c>
       <c r="B8">
-        <v>0.986</v>
+        <v>11.635</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -494,10 +494,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
-        <v>34.9</v>
+        <v>35.9</v>
       </c>
       <c r="B9">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -508,10 +508,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
-        <v>28.2</v>
+        <v>18.3</v>
       </c>
       <c r="B10">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -522,10 +522,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
-        <v>34.6</v>
+        <v>35.5</v>
       </c>
       <c r="B11">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -536,10 +536,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12">
-        <v>35.5</v>
+        <v>52.5</v>
       </c>
       <c r="B12">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -550,10 +550,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13">
-        <v>13.4</v>
+        <v>32.4</v>
       </c>
       <c r="B13">
-        <v>0.021</v>
+        <v>0.78</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -564,10 +564,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14">
-        <v>35.9</v>
+        <v>43</v>
       </c>
       <c r="B14">
-        <v>0.535</v>
+        <v>0.723</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -578,10 +578,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="B15">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
@@ -592,10 +592,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="B16">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
@@ -606,10 +606,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17">
-        <v>30.4</v>
+        <v>19.7</v>
       </c>
       <c r="B17">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C17" t="s">
         <v>4</v>
@@ -620,10 +620,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18">
-        <v>52.5</v>
+        <v>35.8</v>
       </c>
       <c r="B18">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
@@ -634,10 +634,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19">
-        <v>48.1</v>
+        <v>18.1</v>
       </c>
       <c r="B19">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
@@ -648,10 +648,10 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20">
-        <v>40.5</v>
+        <v>36.6</v>
       </c>
       <c r="B20">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C20" t="s">
         <v>4</v>
@@ -662,10 +662,10 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21">
-        <v>34.9</v>
+        <v>50.5</v>
       </c>
       <c r="B21">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C21" t="s">
         <v>4</v>
@@ -676,10 +676,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22">
-        <v>52.2</v>
+        <v>35.6</v>
       </c>
       <c r="B22">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
@@ -690,10 +690,10 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="B23">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24">
-        <v>44.7</v>
+        <v>40.4</v>
       </c>
       <c r="B24">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -718,10 +718,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25">
-        <v>51.6</v>
+        <v>35.2</v>
       </c>
       <c r="B25">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
@@ -732,10 +732,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26">
-        <v>34.9</v>
+        <v>50.5</v>
       </c>
       <c r="B26">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
@@ -746,10 +746,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="B27">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -760,10 +760,10 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28">
-        <v>4.4</v>
+        <v>12.7</v>
       </c>
       <c r="B28">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -774,10 +774,10 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29">
-        <v>57.2</v>
+        <v>5.5</v>
       </c>
       <c r="B29">
-        <v>2.012</v>
+        <v>0.065</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
@@ -788,10 +788,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30">
-        <v>42.8</v>
+        <v>38.7</v>
       </c>
       <c r="B30">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31">
-        <v>41</v>
+        <v>61.3</v>
       </c>
       <c r="B31">
-        <v>0.986</v>
+        <v>11.635</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
@@ -816,10 +816,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32">
-        <v>3.7</v>
+        <v>26.6</v>
       </c>
       <c r="B32">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C32" t="s">
         <v>4</v>
@@ -830,10 +830,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33">
-        <v>51.4</v>
+        <v>32.9</v>
       </c>
       <c r="B33">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C33" t="s">
         <v>4</v>
@@ -844,10 +844,10 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34">
-        <v>34.3</v>
+        <v>35.3</v>
       </c>
       <c r="B34">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35">
-        <v>3.7</v>
+        <v>26.7</v>
       </c>
       <c r="B35">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
@@ -872,10 +872,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36">
-        <v>26.8</v>
+        <v>17.4</v>
       </c>
       <c r="B36">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -886,10 +886,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37">
-        <v>55.1</v>
+        <v>35.2</v>
       </c>
       <c r="B37">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C37" t="s">
         <v>4</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="B38">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C38" t="s">
         <v>4</v>
@@ -914,10 +914,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39">
-        <v>34</v>
+        <v>50.3</v>
       </c>
       <c r="B39">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C39" t="s">
         <v>4</v>
@@ -928,10 +928,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40">
-        <v>33.8</v>
+        <v>34.7</v>
       </c>
       <c r="B40">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C40" t="s">
         <v>4</v>
@@ -942,10 +942,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41">
-        <v>37.6</v>
+        <v>55.9</v>
       </c>
       <c r="B41">
-        <v>0.379</v>
+        <v>4.268</v>
       </c>
       <c r="C41" t="s">
         <v>4</v>
@@ -956,10 +956,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42">
-        <v>60.4</v>
+        <v>5.8</v>
       </c>
       <c r="B42">
-        <v>2.012</v>
+        <v>0.065</v>
       </c>
       <c r="C42" t="s">
         <v>4</v>
@@ -970,10 +970,10 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43">
-        <v>34.5</v>
+        <v>35.4</v>
       </c>
       <c r="B43">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C43" t="s">
         <v>4</v>
@@ -984,10 +984,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44">
-        <v>48.1</v>
+        <v>18.1</v>
       </c>
       <c r="B44">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C44" t="s">
         <v>4</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45">
-        <v>7.5</v>
+        <v>27</v>
       </c>
       <c r="B45">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C45" t="s">
         <v>4</v>
@@ -1012,10 +1012,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46">
-        <v>9.699999999999999</v>
+        <v>36.7</v>
       </c>
       <c r="B46">
-        <v>0.026</v>
+        <v>0.458</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
@@ -1026,10 +1026,10 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47">
-        <v>53.6</v>
+        <v>36.5</v>
       </c>
       <c r="B47">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C47" t="s">
         <v>4</v>
@@ -1040,10 +1040,10 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48">
-        <v>39.4</v>
+        <v>58.9</v>
       </c>
       <c r="B48">
-        <v>0.986</v>
+        <v>11.635</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
@@ -1054,10 +1054,10 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49">
-        <v>47.2</v>
+        <v>30.2</v>
       </c>
       <c r="B49">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C49" t="s">
         <v>4</v>
@@ -1068,10 +1068,10 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50">
-        <v>40.7</v>
+        <v>15.3</v>
       </c>
       <c r="B50">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
@@ -1082,10 +1082,10 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="B51">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C51" t="s">
         <v>4</v>
@@ -1096,10 +1096,10 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52">
-        <v>48.5</v>
+        <v>18.2</v>
       </c>
       <c r="B52">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C52" t="s">
         <v>4</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53">
-        <v>7.1</v>
+        <v>25.7</v>
       </c>
       <c r="B53">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
@@ -1124,10 +1124,10 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54">
-        <v>7.8</v>
+        <v>28.3</v>
       </c>
       <c r="B54">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C54" t="s">
         <v>4</v>
@@ -1138,10 +1138,10 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55">
-        <v>33.6</v>
+        <v>34.5</v>
       </c>
       <c r="B55">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C55" t="s">
         <v>4</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56">
-        <v>53.7</v>
+        <v>36.6</v>
       </c>
       <c r="B56">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C56" t="s">
         <v>4</v>
@@ -1166,10 +1166,10 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57">
-        <v>40</v>
+        <v>59.4</v>
       </c>
       <c r="B57">
-        <v>0.379</v>
+        <v>4.268</v>
       </c>
       <c r="C57" t="s">
         <v>4</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58">
-        <v>3.9</v>
+        <v>28</v>
       </c>
       <c r="B58">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C58" t="s">
         <v>4</v>
@@ -1194,10 +1194,10 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59">
-        <v>31.3</v>
+        <v>18.4</v>
       </c>
       <c r="B59">
-        <v>0.181</v>
+        <v>0.097</v>
       </c>
       <c r="C59" t="s">
         <v>4</v>
@@ -1208,10 +1208,10 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60">
-        <v>37.9</v>
+        <v>56.1</v>
       </c>
       <c r="B60">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C60" t="s">
         <v>4</v>
@@ -1222,10 +1222,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61">
-        <v>58.2</v>
+        <v>39.7</v>
       </c>
       <c r="B61">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C61" t="s">
         <v>4</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62">
-        <v>46.1</v>
+        <v>41.7</v>
       </c>
       <c r="B62">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C62" t="s">
         <v>4</v>
@@ -1250,10 +1250,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63">
-        <v>45.3</v>
+        <v>17</v>
       </c>
       <c r="B63">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C63" t="s">
         <v>4</v>
@@ -1264,10 +1264,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64">
-        <v>4.4</v>
+        <v>12.8</v>
       </c>
       <c r="B64">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
       <c r="C64" t="s">
         <v>4</v>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65">
-        <v>35.5</v>
+        <v>51.4</v>
       </c>
       <c r="B65">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C65" t="s">
         <v>4</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66">
-        <v>4.1</v>
+        <v>29.3</v>
       </c>
       <c r="B66">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C66" t="s">
         <v>4</v>
@@ -1306,10 +1306,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67">
-        <v>34.7</v>
+        <v>51.4</v>
       </c>
       <c r="B67">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C67" t="s">
         <v>4</v>
@@ -1320,10 +1320,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68">
-        <v>6.9</v>
+        <v>25</v>
       </c>
       <c r="B68">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C68" t="s">
         <v>4</v>
@@ -1334,10 +1334,10 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69">
-        <v>33.9</v>
+        <v>21.2</v>
       </c>
       <c r="B69">
-        <v>0.481</v>
+        <v>0.133</v>
       </c>
       <c r="C69" t="s">
         <v>4</v>
@@ -1348,10 +1348,10 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70">
-        <v>3.9</v>
+        <v>11.3</v>
       </c>
       <c r="B70">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
       <c r="C70" t="s">
         <v>4</v>
@@ -1362,10 +1362,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71">
-        <v>37.3</v>
+        <v>23.3</v>
       </c>
       <c r="B71">
-        <v>0.481</v>
+        <v>0.133</v>
       </c>
       <c r="C71" t="s">
         <v>4</v>
@@ -1376,10 +1376,10 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72">
-        <v>33.5</v>
+        <v>49.6</v>
       </c>
       <c r="B72">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C72" t="s">
         <v>4</v>
@@ -1390,10 +1390,10 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73">
-        <v>34.6</v>
+        <v>50</v>
       </c>
       <c r="B73">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C73" t="s">
         <v>4</v>
@@ -1404,10 +1404,10 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74">
-        <v>45.5</v>
+        <v>17.1</v>
       </c>
       <c r="B74">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C74" t="s">
         <v>4</v>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="B75">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C75" t="s">
         <v>4</v>
@@ -1432,10 +1432,10 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76">
-        <v>49.7</v>
+        <v>31.8</v>
       </c>
       <c r="B76">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C76" t="s">
         <v>4</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="B77">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
       <c r="C77" t="s">
         <v>4</v>
@@ -1460,10 +1460,10 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78">
-        <v>32.2</v>
+        <v>33.1</v>
       </c>
       <c r="B78">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C78" t="s">
         <v>4</v>
@@ -1474,10 +1474,10 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79">
-        <v>53.6</v>
+        <v>34.3</v>
       </c>
       <c r="B79">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C79" t="s">
         <v>4</v>
@@ -1488,10 +1488,10 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80">
-        <v>57.4</v>
+        <v>36.7</v>
       </c>
       <c r="B80">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C80" t="s">
         <v>4</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81">
-        <v>35.4</v>
+        <v>42.4</v>
       </c>
       <c r="B81">
-        <v>0.535</v>
+        <v>0.723</v>
       </c>
       <c r="C81" t="s">
         <v>4</v>
@@ -1516,10 +1516,10 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82">
-        <v>60.3</v>
+        <v>5.8</v>
       </c>
       <c r="B82">
-        <v>2.012</v>
+        <v>0.065</v>
       </c>
       <c r="C82" t="s">
         <v>4</v>
@@ -1530,10 +1530,10 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83">
-        <v>37.6</v>
+        <v>54.4</v>
       </c>
       <c r="B83">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C83" t="s">
         <v>4</v>
@@ -1544,10 +1544,10 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84">
-        <v>36</v>
+        <v>43.1</v>
       </c>
       <c r="B84">
-        <v>0.535</v>
+        <v>0.723</v>
       </c>
       <c r="C84" t="s">
         <v>4</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85">
-        <v>31.3</v>
+        <v>32.2</v>
       </c>
       <c r="B85">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C85" t="s">
         <v>4</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86">
-        <v>7.4</v>
+        <v>26.6</v>
       </c>
       <c r="B86">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C86" t="s">
         <v>4</v>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87">
-        <v>39.6</v>
+        <v>59.1</v>
       </c>
       <c r="B87">
-        <v>0.986</v>
+        <v>11.635</v>
       </c>
       <c r="C87" t="s">
         <v>4</v>
@@ -1600,10 +1600,10 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88">
-        <v>7.1</v>
+        <v>25.5</v>
       </c>
       <c r="B88">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C88" t="s">
         <v>4</v>
@@ -1614,10 +1614,10 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89">
-        <v>4.1</v>
+        <v>29.6</v>
       </c>
       <c r="B89">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C89" t="s">
         <v>4</v>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90">
-        <v>7.6</v>
+        <v>27.4</v>
       </c>
       <c r="B90">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C90" t="s">
         <v>4</v>
@@ -1642,10 +1642,10 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91">
-        <v>33.7</v>
+        <v>48.7</v>
       </c>
       <c r="B91">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C91" t="s">
         <v>4</v>
@@ -1656,10 +1656,10 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="B92">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C92" t="s">
         <v>4</v>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93">
-        <v>32.9</v>
+        <v>39.4</v>
       </c>
       <c r="B93">
-        <v>0.535</v>
+        <v>0.723</v>
       </c>
       <c r="C93" t="s">
         <v>4</v>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="B94">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C94" t="s">
         <v>4</v>
@@ -1698,10 +1698,10 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95">
-        <v>8.199999999999999</v>
+        <v>29.5</v>
       </c>
       <c r="B95">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C95" t="s">
         <v>4</v>
@@ -1712,10 +1712,10 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96">
-        <v>33</v>
+        <v>33.9</v>
       </c>
       <c r="B96">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C96" t="s">
         <v>4</v>
@@ -1726,10 +1726,10 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97">
-        <v>9.6</v>
+        <v>36.3</v>
       </c>
       <c r="B97">
-        <v>0.026</v>
+        <v>0.458</v>
       </c>
       <c r="C97" t="s">
         <v>4</v>
@@ -1740,10 +1740,10 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98">
-        <v>4.1</v>
+        <v>11.9</v>
       </c>
       <c r="B98">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
       <c r="C98" t="s">
         <v>4</v>
@@ -1754,10 +1754,10 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99">
-        <v>44.7</v>
+        <v>16.8</v>
       </c>
       <c r="B99">
-        <v>0.9389999999999999</v>
+        <v>0.061</v>
       </c>
       <c r="C99" t="s">
         <v>4</v>
@@ -1768,10 +1768,10 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100">
-        <v>51.4</v>
+        <v>32.9</v>
       </c>
       <c r="B100">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C100" t="s">
         <v>4</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101">
-        <v>27.2</v>
+        <v>17.6</v>
       </c>
       <c r="B101">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C101" t="s">
         <v>4</v>
@@ -1796,10 +1796,10 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102">
-        <v>38.3</v>
+        <v>55.4</v>
       </c>
       <c r="B102">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C102" t="s">
         <v>4</v>
@@ -1810,10 +1810,10 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103">
-        <v>34</v>
+        <v>34.9</v>
       </c>
       <c r="B103">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C103" t="s">
         <v>4</v>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104">
-        <v>35.5</v>
+        <v>51.3</v>
       </c>
       <c r="B104">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C104" t="s">
         <v>4</v>
@@ -1838,10 +1838,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105">
-        <v>4.1</v>
+        <v>29.6</v>
       </c>
       <c r="B105">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C105" t="s">
         <v>4</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106">
-        <v>34</v>
+        <v>50.3</v>
       </c>
       <c r="B106">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C106" t="s">
         <v>4</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="B107">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C107" t="s">
         <v>4</v>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108">
-        <v>33.2</v>
+        <v>39.8</v>
       </c>
       <c r="B108">
-        <v>0.535</v>
+        <v>0.723</v>
       </c>
       <c r="C108" t="s">
         <v>4</v>
@@ -1894,10 +1894,10 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109">
-        <v>31.9</v>
+        <v>19.9</v>
       </c>
       <c r="B109">
-        <v>0.481</v>
+        <v>0.133</v>
       </c>
       <c r="C109" t="s">
         <v>4</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110">
-        <v>4.1</v>
+        <v>29.2</v>
       </c>
       <c r="B110">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C110" t="s">
         <v>4</v>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111">
-        <v>42.5</v>
+        <v>38.4</v>
       </c>
       <c r="B111">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C111" t="s">
         <v>4</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112">
-        <v>37.4</v>
+        <v>55.6</v>
       </c>
       <c r="B112">
-        <v>0.379</v>
+        <v>4.268</v>
       </c>
       <c r="C112" t="s">
         <v>4</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113">
-        <v>31.8</v>
+        <v>18.8</v>
       </c>
       <c r="B113">
-        <v>0.181</v>
+        <v>0.097</v>
       </c>
       <c r="C113" t="s">
         <v>4</v>
@@ -1964,10 +1964,10 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114">
-        <v>36.7</v>
+        <v>54.3</v>
       </c>
       <c r="B114">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C114" t="s">
         <v>4</v>
@@ -1978,10 +1978,10 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115">
-        <v>3.6</v>
+        <v>25.8</v>
       </c>
       <c r="B115">
-        <v>0.017</v>
+        <v>0.605</v>
       </c>
       <c r="C115" t="s">
         <v>4</v>
@@ -1992,10 +1992,10 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116">
-        <v>32.2</v>
+        <v>19</v>
       </c>
       <c r="B116">
-        <v>0.181</v>
+        <v>0.097</v>
       </c>
       <c r="C116" t="s">
         <v>4</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117">
-        <v>13.2</v>
+        <v>31.8</v>
       </c>
       <c r="B117">
-        <v>0.021</v>
+        <v>0.78</v>
       </c>
       <c r="C117" t="s">
         <v>4</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118">
-        <v>43.6</v>
+        <v>39.4</v>
       </c>
       <c r="B118">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C118" t="s">
         <v>4</v>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119">
-        <v>36.6</v>
+        <v>54.4</v>
       </c>
       <c r="B119">
-        <v>0.379</v>
+        <v>4.268</v>
       </c>
       <c r="C119" t="s">
         <v>4</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120">
-        <v>4.2</v>
+        <v>12.2</v>
       </c>
       <c r="B120">
-        <v>0.156</v>
+        <v>0.042</v>
       </c>
       <c r="C120" t="s">
         <v>4</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121">
-        <v>52.2</v>
+        <v>35.6</v>
       </c>
       <c r="B121">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C121" t="s">
         <v>4</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122">
-        <v>32.4</v>
+        <v>47.9</v>
       </c>
       <c r="B122">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C122" t="s">
         <v>4</v>
@@ -2090,10 +2090,10 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123">
-        <v>65.3</v>
+        <v>6.3</v>
       </c>
       <c r="B123">
-        <v>2.012</v>
+        <v>0.065</v>
       </c>
       <c r="C123" t="s">
         <v>4</v>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124">
-        <v>35.8</v>
+        <v>51.8</v>
       </c>
       <c r="B124">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C124" t="s">
         <v>4</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125">
-        <v>57.2</v>
+        <v>36.6</v>
       </c>
       <c r="B125">
-        <v>0.803</v>
+        <v>1.358</v>
       </c>
       <c r="C125" t="s">
         <v>4</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126">
-        <v>32.2</v>
+        <v>33.1</v>
       </c>
       <c r="B126">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C126" t="s">
         <v>4</v>
@@ -2146,10 +2146,10 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127">
-        <v>35</v>
+        <v>21.8</v>
       </c>
       <c r="B127">
-        <v>0.481</v>
+        <v>0.133</v>
       </c>
       <c r="C127" t="s">
         <v>4</v>
@@ -2160,10 +2160,10 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128">
-        <v>33.3</v>
+        <v>48.2</v>
       </c>
       <c r="B128">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C128" t="s">
         <v>4</v>
@@ -2174,10 +2174,10 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129">
-        <v>38.9</v>
+        <v>57.9</v>
       </c>
       <c r="B129">
-        <v>0.379</v>
+        <v>4.268</v>
       </c>
       <c r="C129" t="s">
         <v>4</v>
@@ -2188,10 +2188,10 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130">
-        <v>7.1</v>
+        <v>25.4</v>
       </c>
       <c r="B130">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C130" t="s">
         <v>4</v>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131">
-        <v>29.3</v>
+        <v>43.4</v>
       </c>
       <c r="B131">
-        <v>0.404</v>
+        <v>1.554</v>
       </c>
       <c r="C131" t="s">
         <v>4</v>
@@ -2216,10 +2216,10 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132">
-        <v>36.3</v>
+        <v>54.2</v>
       </c>
       <c r="B132">
-        <v>0.986</v>
+        <v>11.635</v>
       </c>
       <c r="C132" t="s">
         <v>4</v>
@@ -2230,10 +2230,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133">
-        <v>28.6</v>
+        <v>18.6</v>
       </c>
       <c r="B133">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C133" t="s">
         <v>4</v>
@@ -2244,10 +2244,10 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134">
-        <v>9.300000000000001</v>
+        <v>35.4</v>
       </c>
       <c r="B134">
-        <v>0.026</v>
+        <v>0.458</v>
       </c>
       <c r="C134" t="s">
         <v>4</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135">
-        <v>7.4</v>
+        <v>26.6</v>
       </c>
       <c r="B135">
-        <v>0.027</v>
+        <v>0.251</v>
       </c>
       <c r="C135" t="s">
         <v>4</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="B136">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C136" t="s">
         <v>4</v>
@@ -2286,10 +2286,10 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137">
-        <v>38.3</v>
+        <v>23.9</v>
       </c>
       <c r="B137">
-        <v>0.481</v>
+        <v>0.133</v>
       </c>
       <c r="C137" t="s">
         <v>4</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138">
-        <v>36.5</v>
+        <v>52.7</v>
       </c>
       <c r="B138">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C138" t="s">
         <v>4</v>
@@ -2314,10 +2314,10 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139">
-        <v>32.5</v>
+        <v>19.1</v>
       </c>
       <c r="B139">
-        <v>0.181</v>
+        <v>0.097</v>
       </c>
       <c r="C139" t="s">
         <v>4</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="B140">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C140" t="s">
         <v>4</v>
@@ -2342,10 +2342,10 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141">
-        <v>32.5</v>
+        <v>20.3</v>
       </c>
       <c r="B141">
-        <v>0.481</v>
+        <v>0.133</v>
       </c>
       <c r="C141" t="s">
         <v>4</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142">
-        <v>59.4</v>
+        <v>40.5</v>
       </c>
       <c r="B142">
-        <v>1.264</v>
+        <v>0.819</v>
       </c>
       <c r="C142" t="s">
         <v>4</v>
@@ -2370,10 +2370,10 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143">
-        <v>63.6</v>
+        <v>6.1</v>
       </c>
       <c r="B143">
-        <v>2.012</v>
+        <v>0.065</v>
       </c>
       <c r="C143" t="s">
         <v>4</v>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144">
-        <v>34.8</v>
+        <v>35.7</v>
       </c>
       <c r="B144">
-        <v>0.361</v>
+        <v>0.704</v>
       </c>
       <c r="C144" t="s">
         <v>4</v>
@@ -2398,10 +2398,10 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145">
-        <v>29.7</v>
+        <v>19.2</v>
       </c>
       <c r="B145">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C145" t="s">
         <v>4</v>
@@ -2412,10 +2412,10 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146">
-        <v>28.1</v>
+        <v>18.2</v>
       </c>
       <c r="B146">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C146" t="s">
         <v>4</v>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="B147">
-        <v>0.057</v>
+        <v>0.055</v>
       </c>
       <c r="C147" t="s">
         <v>4</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148">
-        <v>27.7</v>
+        <v>18</v>
       </c>
       <c r="B148">
-        <v>0.243</v>
+        <v>0.183</v>
       </c>
       <c r="C148" t="s">
         <v>4</v>
@@ -2454,10 +2454,10 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149">
-        <v>39</v>
+        <v>56.5</v>
       </c>
       <c r="B149">
-        <v>0.32</v>
+        <v>3.076</v>
       </c>
       <c r="C149" t="s">
         <v>4</v>
@@ -2468,10 +2468,10 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150">
-        <v>45.4</v>
+        <v>41</v>
       </c>
       <c r="B150">
-        <v>0.72</v>
+        <v>0.735</v>
       </c>
       <c r="C150" t="s">
         <v>4</v>
@@ -2482,10 +2482,10 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151">
-        <v>39.4</v>
+        <v>58.9</v>
       </c>
       <c r="B151">
-        <v>0.986</v>
+        <v>11.635</v>
       </c>
       <c r="C151" t="s">
         <v>4</v>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152">
-        <v>20.3</v>
+        <v>14</v>
       </c>
       <c r="B152">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C152" t="s">
         <v>5</v>
@@ -2510,10 +2510,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153">
-        <v>32.9</v>
+        <v>14.7</v>
       </c>
       <c r="B153">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C153" t="s">
         <v>5</v>
@@ -2524,10 +2524,10 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154">
-        <v>17.1</v>
+        <v>12.6</v>
       </c>
       <c r="B154">
-        <v>0.418</v>
+        <v>0.381</v>
       </c>
       <c r="C154" t="s">
         <v>5</v>
@@ -2538,10 +2538,10 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155">
-        <v>11</v>
+        <v>13.3</v>
       </c>
       <c r="B155">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C155" t="s">
         <v>5</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="B156">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C156" t="s">
         <v>5</v>
@@ -2566,10 +2566,10 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157">
-        <v>17.3</v>
+        <v>20.7</v>
       </c>
       <c r="B157">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C157" t="s">
         <v>5</v>
@@ -2580,10 +2580,10 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158">
-        <v>20.9</v>
+        <v>14.5</v>
       </c>
       <c r="B158">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C158" t="s">
         <v>5</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159">
-        <v>23.1</v>
+        <v>26.7</v>
       </c>
       <c r="B159">
-        <v>0.856</v>
+        <v>0.611</v>
       </c>
       <c r="C159" t="s">
         <v>5</v>
@@ -2608,10 +2608,10 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160">
-        <v>25.7</v>
+        <v>27.1</v>
       </c>
       <c r="B160">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C160" t="s">
         <v>5</v>
@@ -2622,10 +2622,10 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="B161">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C161" t="s">
         <v>5</v>
@@ -2636,10 +2636,10 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162">
-        <v>16.7</v>
+        <v>29.5</v>
       </c>
       <c r="B162">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C162" t="s">
         <v>5</v>
@@ -2650,10 +2650,10 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163">
-        <v>22.9</v>
+        <v>23.7</v>
       </c>
       <c r="B163">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C163" t="s">
         <v>5</v>
@@ -2664,10 +2664,10 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="B164">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C164" t="s">
         <v>5</v>
@@ -2678,10 +2678,10 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165">
-        <v>15.5</v>
+        <v>27.3</v>
       </c>
       <c r="B165">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C165" t="s">
         <v>5</v>
@@ -2692,10 +2692,10 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166">
-        <v>9.699999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="B166">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C166" t="s">
         <v>5</v>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167">
-        <v>18.2</v>
+        <v>13.4</v>
       </c>
       <c r="B167">
-        <v>0.418</v>
+        <v>0.381</v>
       </c>
       <c r="C167" t="s">
         <v>5</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168">
-        <v>24</v>
+        <v>26.1</v>
       </c>
       <c r="B168">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C168" t="s">
         <v>5</v>
@@ -2734,10 +2734,10 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169">
-        <v>23</v>
+        <v>26.6</v>
       </c>
       <c r="B169">
-        <v>0.856</v>
+        <v>0.611</v>
       </c>
       <c r="C169" t="s">
         <v>5</v>
@@ -2748,10 +2748,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170">
-        <v>38.6</v>
+        <v>10</v>
       </c>
       <c r="B170">
-        <v>3.455</v>
+        <v>0.094</v>
       </c>
       <c r="C170" t="s">
         <v>5</v>
@@ -2762,10 +2762,10 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="B171">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C171" t="s">
         <v>5</v>
@@ -2776,10 +2776,10 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172">
-        <v>25.2</v>
+        <v>26.6</v>
       </c>
       <c r="B172">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C172" t="s">
         <v>5</v>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173">
-        <v>17.7</v>
+        <v>28.3</v>
       </c>
       <c r="B173">
-        <v>0.633</v>
+        <v>1.499</v>
       </c>
       <c r="C173" t="s">
         <v>5</v>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174">
-        <v>30.8</v>
+        <v>13.7</v>
       </c>
       <c r="B174">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C174" t="s">
         <v>5</v>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175">
-        <v>18.4</v>
+        <v>29.6</v>
       </c>
       <c r="B175">
-        <v>0.633</v>
+        <v>1.499</v>
       </c>
       <c r="C175" t="s">
         <v>5</v>
@@ -2832,10 +2832,10 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176">
-        <v>14.7</v>
+        <v>16.5</v>
       </c>
       <c r="B176">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C176" t="s">
         <v>5</v>
@@ -2846,10 +2846,10 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
       <c r="B177">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C177" t="s">
         <v>5</v>
@@ -2860,10 +2860,10 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178">
-        <v>26.4</v>
+        <v>29.2</v>
       </c>
       <c r="B178">
-        <v>1.48</v>
+        <v>0.988</v>
       </c>
       <c r="C178" t="s">
         <v>5</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179">
-        <v>21.3</v>
+        <v>24.7</v>
       </c>
       <c r="B179">
-        <v>0.856</v>
+        <v>0.611</v>
       </c>
       <c r="C179" t="s">
         <v>5</v>
@@ -2888,10 +2888,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180">
-        <v>19.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="B180">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C180" t="s">
         <v>5</v>
@@ -2902,10 +2902,10 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181">
-        <v>16.8</v>
+        <v>12.4</v>
       </c>
       <c r="B181">
-        <v>0.418</v>
+        <v>0.381</v>
       </c>
       <c r="C181" t="s">
         <v>5</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182">
-        <v>18.7</v>
+        <v>7.8</v>
       </c>
       <c r="B182">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C182" t="s">
         <v>5</v>
@@ -2930,10 +2930,10 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="B183">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C183" t="s">
         <v>5</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="B184">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C184" t="s">
         <v>5</v>
@@ -2958,10 +2958,10 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="B185">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C185" t="s">
         <v>5</v>
@@ -2972,10 +2972,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186">
-        <v>26.7</v>
+        <v>23.8</v>
       </c>
       <c r="B186">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C186" t="s">
         <v>5</v>
@@ -2986,10 +2986,10 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187">
-        <v>14</v>
+        <v>18.1</v>
       </c>
       <c r="B187">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C187" t="s">
         <v>5</v>
@@ -3000,10 +3000,10 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188">
-        <v>17.9</v>
+        <v>13.2</v>
       </c>
       <c r="B188">
-        <v>0.418</v>
+        <v>0.381</v>
       </c>
       <c r="C188" t="s">
         <v>5</v>
@@ -3014,10 +3014,10 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="B189">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C189" t="s">
         <v>5</v>
@@ -3028,10 +3028,10 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190">
-        <v>16.4</v>
+        <v>19.6</v>
       </c>
       <c r="B190">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C190" t="s">
         <v>5</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="B191">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C191" t="s">
         <v>5</v>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192">
-        <v>24.4</v>
+        <v>26.5</v>
       </c>
       <c r="B192">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C192" t="s">
         <v>5</v>
@@ -3070,10 +3070,10 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193">
-        <v>17.6</v>
+        <v>21</v>
       </c>
       <c r="B193">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C193" t="s">
         <v>5</v>
@@ -3084,10 +3084,10 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194">
-        <v>16.8</v>
+        <v>20</v>
       </c>
       <c r="B194">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C194" t="s">
         <v>5</v>
@@ -3098,10 +3098,10 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195">
-        <v>27</v>
+        <v>28.4</v>
       </c>
       <c r="B195">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C195" t="s">
         <v>5</v>
@@ -3112,10 +3112,10 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196">
-        <v>34.7</v>
+        <v>15.5</v>
       </c>
       <c r="B196">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C196" t="s">
         <v>5</v>
@@ -3126,10 +3126,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197">
-        <v>28.2</v>
+        <v>29.8</v>
       </c>
       <c r="B197">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C197" t="s">
         <v>5</v>
@@ -3140,10 +3140,10 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="B198">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C198" t="s">
         <v>5</v>
@@ -3154,10 +3154,10 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199">
-        <v>16.5</v>
+        <v>29.2</v>
       </c>
       <c r="B199">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C199" t="s">
         <v>5</v>
@@ -3168,10 +3168,10 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200">
-        <v>26</v>
+        <v>27.5</v>
       </c>
       <c r="B200">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C200" t="s">
         <v>5</v>
@@ -3182,10 +3182,10 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201">
-        <v>21.2</v>
+        <v>8.9</v>
       </c>
       <c r="B201">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C201" t="s">
         <v>5</v>
@@ -3196,10 +3196,10 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202">
-        <v>31.7</v>
+        <v>14.1</v>
       </c>
       <c r="B202">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C202" t="s">
         <v>5</v>
@@ -3210,10 +3210,10 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203">
-        <v>21.7</v>
+        <v>25</v>
       </c>
       <c r="B203">
-        <v>0.856</v>
+        <v>0.611</v>
       </c>
       <c r="C203" t="s">
         <v>5</v>
@@ -3224,10 +3224,10 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204">
-        <v>37.1</v>
+        <v>16.5</v>
       </c>
       <c r="B204">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C204" t="s">
         <v>5</v>
@@ -3238,10 +3238,10 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205">
-        <v>15.1</v>
+        <v>19.5</v>
       </c>
       <c r="B205">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C205" t="s">
         <v>5</v>
@@ -3252,10 +3252,10 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206">
-        <v>35.2</v>
+        <v>9.1</v>
       </c>
       <c r="B206">
-        <v>3.455</v>
+        <v>0.094</v>
       </c>
       <c r="C206" t="s">
         <v>5</v>
@@ -3266,10 +3266,10 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207">
-        <v>16.5</v>
+        <v>29.1</v>
       </c>
       <c r="B207">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C207" t="s">
         <v>5</v>
@@ -3280,10 +3280,10 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208">
-        <v>10.9</v>
+        <v>13.1</v>
       </c>
       <c r="B208">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C208" t="s">
         <v>5</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="B209">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C209" t="s">
         <v>5</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="B210">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C210" t="s">
         <v>5</v>
@@ -3322,10 +3322,10 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211">
-        <v>17.7</v>
+        <v>28.3</v>
       </c>
       <c r="B211">
-        <v>0.633</v>
+        <v>1.499</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -3336,10 +3336,10 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212">
-        <v>15.5</v>
+        <v>12.9</v>
       </c>
       <c r="B212">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213">
-        <v>10.8</v>
+        <v>13</v>
       </c>
       <c r="B213">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214">
-        <v>17.7</v>
+        <v>31.2</v>
       </c>
       <c r="B214">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C214" t="s">
         <v>5</v>
@@ -3378,10 +3378,10 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="B215">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
@@ -3392,10 +3392,10 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216">
-        <v>24.4</v>
+        <v>21.7</v>
       </c>
       <c r="B216">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C216" t="s">
         <v>5</v>
@@ -3406,10 +3406,10 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217">
-        <v>27.1</v>
+        <v>30</v>
       </c>
       <c r="B217">
-        <v>1.48</v>
+        <v>0.988</v>
       </c>
       <c r="C217" t="s">
         <v>5</v>
@@ -3420,10 +3420,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218">
-        <v>16.3</v>
+        <v>19.5</v>
       </c>
       <c r="B218">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C218" t="s">
         <v>5</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219">
-        <v>8.6</v>
+        <v>11.3</v>
       </c>
       <c r="B219">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C219" t="s">
         <v>5</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220">
-        <v>25.9</v>
+        <v>27.4</v>
       </c>
       <c r="B220">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C220" t="s">
         <v>5</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221">
-        <v>21</v>
+        <v>14.6</v>
       </c>
       <c r="B221">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C221" t="s">
         <v>5</v>
@@ -3476,10 +3476,10 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222">
-        <v>15.7</v>
+        <v>27.7</v>
       </c>
       <c r="B222">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C222" t="s">
         <v>5</v>
@@ -3490,10 +3490,10 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223">
-        <v>23.1</v>
+        <v>25.1</v>
       </c>
       <c r="B223">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C223" t="s">
         <v>5</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224">
-        <v>20.4</v>
+        <v>14.1</v>
       </c>
       <c r="B224">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C224" t="s">
         <v>5</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225">
-        <v>25.1</v>
+        <v>22.3</v>
       </c>
       <c r="B225">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C225" t="s">
         <v>5</v>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226">
-        <v>15.2</v>
+        <v>17.1</v>
       </c>
       <c r="B226">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C226" t="s">
         <v>5</v>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="B227">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C227" t="s">
         <v>5</v>
@@ -3560,10 +3560,10 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="B228">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C228" t="s">
         <v>5</v>
@@ -3574,10 +3574,10 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229">
-        <v>8.800000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="B229">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C229" t="s">
         <v>5</v>
@@ -3588,10 +3588,10 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230">
-        <v>20.3</v>
+        <v>14.1</v>
       </c>
       <c r="B230">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C230" t="s">
         <v>5</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231">
-        <v>9.699999999999999</v>
+        <v>12.8</v>
       </c>
       <c r="B231">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C231" t="s">
         <v>5</v>
@@ -3616,10 +3616,10 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="B232">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C232" t="s">
         <v>5</v>
@@ -3630,10 +3630,10 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233">
-        <v>9</v>
+        <v>11.9</v>
       </c>
       <c r="B233">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C233" t="s">
         <v>5</v>
@@ -3644,10 +3644,10 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="B234">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C234" t="s">
         <v>5</v>
@@ -3658,10 +3658,10 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235">
-        <v>24.6</v>
+        <v>21.9</v>
       </c>
       <c r="B235">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C235" t="s">
         <v>5</v>
@@ -3672,10 +3672,10 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236">
-        <v>16.7</v>
+        <v>26.7</v>
       </c>
       <c r="B236">
-        <v>0.633</v>
+        <v>1.499</v>
       </c>
       <c r="C236" t="s">
         <v>5</v>
@@ -3686,10 +3686,10 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="B237">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C237" t="s">
         <v>5</v>
@@ -3700,10 +3700,10 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238">
-        <v>14.7</v>
+        <v>16.5</v>
       </c>
       <c r="B238">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C238" t="s">
         <v>5</v>
@@ -3714,10 +3714,10 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239">
-        <v>11.7</v>
+        <v>14.2</v>
       </c>
       <c r="B239">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C239" t="s">
         <v>5</v>
@@ -3728,10 +3728,10 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="B240">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C240" t="s">
         <v>5</v>
@@ -3742,10 +3742,10 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241">
-        <v>24.4</v>
+        <v>21.7</v>
       </c>
       <c r="B241">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C241" t="s">
         <v>5</v>
@@ -3756,10 +3756,10 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242">
-        <v>15.9</v>
+        <v>13.2</v>
       </c>
       <c r="B242">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C242" t="s">
         <v>5</v>
@@ -3770,10 +3770,10 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243">
-        <v>11.5</v>
+        <v>13.9</v>
       </c>
       <c r="B243">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C243" t="s">
         <v>5</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244">
-        <v>28.9</v>
+        <v>31.9</v>
       </c>
       <c r="B244">
-        <v>1.48</v>
+        <v>0.988</v>
       </c>
       <c r="C244" t="s">
         <v>5</v>
@@ -3798,10 +3798,10 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="B245">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C245" t="s">
         <v>5</v>
@@ -3812,10 +3812,10 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246">
-        <v>19.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="B246">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C246" t="s">
         <v>5</v>
@@ -3826,10 +3826,10 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247">
-        <v>15.7</v>
+        <v>13</v>
       </c>
       <c r="B247">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C247" t="s">
         <v>5</v>
@@ -3840,10 +3840,10 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248">
-        <v>24.1</v>
+        <v>26.2</v>
       </c>
       <c r="B248">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C248" t="s">
         <v>5</v>
@@ -3854,10 +3854,10 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249">
-        <v>25</v>
+        <v>25.9</v>
       </c>
       <c r="B249">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C249" t="s">
         <v>5</v>
@@ -3868,10 +3868,10 @@
     </row>
     <row r="250" spans="1:4">
       <c r="A250">
-        <v>32.9</v>
+        <v>8.5</v>
       </c>
       <c r="B250">
-        <v>3.455</v>
+        <v>0.094</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
@@ -3882,10 +3882,10 @@
     </row>
     <row r="251" spans="1:4">
       <c r="A251">
-        <v>14.7</v>
+        <v>16.5</v>
       </c>
       <c r="B251">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C251" t="s">
         <v>5</v>
@@ -3896,10 +3896,10 @@
     </row>
     <row r="252" spans="1:4">
       <c r="A252">
-        <v>14.7</v>
+        <v>12.2</v>
       </c>
       <c r="B252">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C252" t="s">
         <v>5</v>
@@ -3910,10 +3910,10 @@
     </row>
     <row r="253" spans="1:4">
       <c r="A253">
-        <v>26</v>
+        <v>23.1</v>
       </c>
       <c r="B253">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C253" t="s">
         <v>5</v>
@@ -3924,10 +3924,10 @@
     </row>
     <row r="254" spans="1:4">
       <c r="A254">
-        <v>16.9</v>
+        <v>14</v>
       </c>
       <c r="B254">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C254" t="s">
         <v>5</v>
@@ -3938,10 +3938,10 @@
     </row>
     <row r="255" spans="1:4">
       <c r="A255">
-        <v>16.9</v>
+        <v>12.5</v>
       </c>
       <c r="B255">
-        <v>0.418</v>
+        <v>0.381</v>
       </c>
       <c r="C255" t="s">
         <v>5</v>
@@ -3952,10 +3952,10 @@
     </row>
     <row r="256" spans="1:4">
       <c r="A256">
-        <v>14.3</v>
+        <v>18.5</v>
       </c>
       <c r="B256">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C256" t="s">
         <v>5</v>
@@ -3966,10 +3966,10 @@
     </row>
     <row r="257" spans="1:4">
       <c r="A257">
-        <v>27.4</v>
+        <v>30.3</v>
       </c>
       <c r="B257">
-        <v>1.48</v>
+        <v>0.988</v>
       </c>
       <c r="C257" t="s">
         <v>5</v>
@@ -3980,10 +3980,10 @@
     </row>
     <row r="258" spans="1:4">
       <c r="A258">
-        <v>25.6</v>
+        <v>27</v>
       </c>
       <c r="B258">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C258" t="s">
         <v>5</v>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="259" spans="1:4">
       <c r="A259">
-        <v>22.2</v>
+        <v>24.1</v>
       </c>
       <c r="B259">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C259" t="s">
         <v>5</v>
@@ -4008,10 +4008,10 @@
     </row>
     <row r="260" spans="1:4">
       <c r="A260">
-        <v>36.8</v>
+        <v>16.4</v>
       </c>
       <c r="B260">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C260" t="s">
         <v>5</v>
@@ -4022,10 +4022,10 @@
     </row>
     <row r="261" spans="1:4">
       <c r="A261">
-        <v>35.7</v>
+        <v>15.9</v>
       </c>
       <c r="B261">
-        <v>3.093</v>
+        <v>0.436</v>
       </c>
       <c r="C261" t="s">
         <v>5</v>
@@ -4036,10 +4036,10 @@
     </row>
     <row r="262" spans="1:4">
       <c r="A262">
-        <v>14.3</v>
+        <v>18.5</v>
       </c>
       <c r="B262">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
@@ -4050,10 +4050,10 @@
     </row>
     <row r="263" spans="1:4">
       <c r="A263">
-        <v>19.4</v>
+        <v>8.1</v>
       </c>
       <c r="B263">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C263" t="s">
         <v>5</v>
@@ -4064,10 +4064,10 @@
     </row>
     <row r="264" spans="1:4">
       <c r="A264">
-        <v>26.3</v>
+        <v>27.8</v>
       </c>
       <c r="B264">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C264" t="s">
         <v>5</v>
@@ -4078,10 +4078,10 @@
     </row>
     <row r="265" spans="1:4">
       <c r="A265">
-        <v>18.9</v>
+        <v>7.9</v>
       </c>
       <c r="B265">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C265" t="s">
         <v>5</v>
@@ -4092,10 +4092,10 @@
     </row>
     <row r="266" spans="1:4">
       <c r="A266">
-        <v>9.6</v>
+        <v>12.6</v>
       </c>
       <c r="B266">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C266" t="s">
         <v>5</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="267" spans="1:4">
       <c r="A267">
-        <v>15.4</v>
+        <v>27.1</v>
       </c>
       <c r="B267">
-        <v>0.372</v>
+        <v>0.464</v>
       </c>
       <c r="C267" t="s">
         <v>5</v>
@@ -4120,10 +4120,10 @@
     </row>
     <row r="268" spans="1:4">
       <c r="A268">
-        <v>18.6</v>
+        <v>12.9</v>
       </c>
       <c r="B268">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C268" t="s">
         <v>5</v>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="269" spans="1:4">
       <c r="A269">
-        <v>15.2</v>
+        <v>12.6</v>
       </c>
       <c r="B269">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="270" spans="1:4">
       <c r="A270">
-        <v>19.1</v>
+        <v>8</v>
       </c>
       <c r="B270">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C270" t="s">
         <v>5</v>
@@ -4162,10 +4162,10 @@
     </row>
     <row r="271" spans="1:4">
       <c r="A271">
-        <v>23.2</v>
+        <v>20.7</v>
       </c>
       <c r="B271">
-        <v>1.06</v>
+        <v>0.472</v>
       </c>
       <c r="C271" t="s">
         <v>5</v>
@@ -4176,10 +4176,10 @@
     </row>
     <row r="272" spans="1:4">
       <c r="A272">
-        <v>21.1</v>
+        <v>22.9</v>
       </c>
       <c r="B272">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C272" t="s">
         <v>5</v>
@@ -4190,10 +4190,10 @@
     </row>
     <row r="273" spans="1:4">
       <c r="A273">
-        <v>11.3</v>
+        <v>13.6</v>
       </c>
       <c r="B273">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C273" t="s">
         <v>5</v>
@@ -4204,10 +4204,10 @@
     </row>
     <row r="274" spans="1:4">
       <c r="A274">
-        <v>10.1</v>
+        <v>13.3</v>
       </c>
       <c r="B274">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C274" t="s">
         <v>5</v>
@@ -4218,10 +4218,10 @@
     </row>
     <row r="275" spans="1:4">
       <c r="A275">
-        <v>15.7</v>
+        <v>20.3</v>
       </c>
       <c r="B275">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C275" t="s">
         <v>5</v>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="276" spans="1:4">
       <c r="A276">
-        <v>9.4</v>
+        <v>12.3</v>
       </c>
       <c r="B276">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C276" t="s">
         <v>5</v>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="277" spans="1:4">
       <c r="A277">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="B277">
-        <v>0.845</v>
+        <v>0.74</v>
       </c>
       <c r="C277" t="s">
         <v>5</v>
@@ -4260,10 +4260,10 @@
     </row>
     <row r="278" spans="1:4">
       <c r="A278">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="B278">
-        <v>0.802</v>
+        <v>0.278</v>
       </c>
       <c r="C278" t="s">
         <v>5</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="279" spans="1:4">
       <c r="A279">
-        <v>22.1</v>
+        <v>25.6</v>
       </c>
       <c r="B279">
-        <v>0.856</v>
+        <v>0.611</v>
       </c>
       <c r="C279" t="s">
         <v>5</v>
@@ -4288,10 +4288,10 @@
     </row>
     <row r="280" spans="1:4">
       <c r="A280">
-        <v>24.4</v>
+        <v>26.5</v>
       </c>
       <c r="B280">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C280" t="s">
         <v>5</v>
@@ -4302,10 +4302,10 @@
     </row>
     <row r="281" spans="1:4">
       <c r="A281">
-        <v>36.6</v>
+        <v>9.5</v>
       </c>
       <c r="B281">
-        <v>3.455</v>
+        <v>0.094</v>
       </c>
       <c r="C281" t="s">
         <v>5</v>
@@ -4316,10 +4316,10 @@
     </row>
     <row r="282" spans="1:4">
       <c r="A282">
-        <v>13.1</v>
+        <v>14.7</v>
       </c>
       <c r="B282">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C282" t="s">
         <v>5</v>
@@ -4330,10 +4330,10 @@
     </row>
     <row r="283" spans="1:4">
       <c r="A283">
-        <v>28.3</v>
+        <v>29.9</v>
       </c>
       <c r="B283">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C283" t="s">
         <v>5</v>
@@ -4344,10 +4344,10 @@
     </row>
     <row r="284" spans="1:4">
       <c r="A284">
-        <v>20.4</v>
+        <v>8.6</v>
       </c>
       <c r="B284">
-        <v>0.868</v>
+        <v>0.112</v>
       </c>
       <c r="C284" t="s">
         <v>5</v>
@@ -4358,10 +4358,10 @@
     </row>
     <row r="285" spans="1:4">
       <c r="A285">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B285">
-        <v>0.994</v>
+        <v>0.788</v>
       </c>
       <c r="C285" t="s">
         <v>5</v>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="286" spans="1:4">
       <c r="A286">
-        <v>11.1</v>
+        <v>13.4</v>
       </c>
       <c r="B286">
-        <v>0.107</v>
+        <v>0.309</v>
       </c>
       <c r="C286" t="s">
         <v>5</v>
@@ -4386,10 +4386,10 @@
     </row>
     <row r="287" spans="1:4">
       <c r="A287">
-        <v>13.3</v>
+        <v>17.2</v>
       </c>
       <c r="B287">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C287" t="s">
         <v>5</v>
@@ -4400,10 +4400,10 @@
     </row>
     <row r="288" spans="1:4">
       <c r="A288">
-        <v>20.8</v>
+        <v>14.4</v>
       </c>
       <c r="B288">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C288" t="s">
         <v>5</v>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="289" spans="1:4">
       <c r="A289">
-        <v>13</v>
+        <v>14.7</v>
       </c>
       <c r="B289">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C289" t="s">
         <v>5</v>
@@ -4428,10 +4428,10 @@
     </row>
     <row r="290" spans="1:4">
       <c r="A290">
-        <v>17.7</v>
+        <v>21.2</v>
       </c>
       <c r="B290">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C290" t="s">
         <v>5</v>
@@ -4442,10 +4442,10 @@
     </row>
     <row r="291" spans="1:4">
       <c r="A291">
-        <v>27.3</v>
+        <v>28.8</v>
       </c>
       <c r="B291">
-        <v>0.6909999999999999</v>
+        <v>1.575</v>
       </c>
       <c r="C291" t="s">
         <v>5</v>
@@ -4456,10 +4456,10 @@
     </row>
     <row r="292" spans="1:4">
       <c r="A292">
-        <v>24.9</v>
+        <v>27.5</v>
       </c>
       <c r="B292">
-        <v>1.48</v>
+        <v>0.988</v>
       </c>
       <c r="C292" t="s">
         <v>5</v>
@@ -4470,10 +4470,10 @@
     </row>
     <row r="293" spans="1:4">
       <c r="A293">
-        <v>16.6</v>
+        <v>19.8</v>
       </c>
       <c r="B293">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C293" t="s">
         <v>5</v>
@@ -4484,10 +4484,10 @@
     </row>
     <row r="294" spans="1:4">
       <c r="A294">
-        <v>14.8</v>
+        <v>16.7</v>
       </c>
       <c r="B294">
-        <v>0.111</v>
+        <v>0.172</v>
       </c>
       <c r="C294" t="s">
         <v>5</v>
@@ -4498,10 +4498,10 @@
     </row>
     <row r="295" spans="1:4">
       <c r="A295">
-        <v>17.1</v>
+        <v>20.4</v>
       </c>
       <c r="B295">
-        <v>0.382</v>
+        <v>0.355</v>
       </c>
       <c r="C295" t="s">
         <v>5</v>
@@ -4512,10 +4512,10 @@
     </row>
     <row r="296" spans="1:4">
       <c r="A296">
-        <v>21.8</v>
+        <v>15.1</v>
       </c>
       <c r="B296">
-        <v>0.843</v>
+        <v>0.32</v>
       </c>
       <c r="C296" t="s">
         <v>5</v>
@@ -4526,10 +4526,10 @@
     </row>
     <row r="297" spans="1:4">
       <c r="A297">
-        <v>9.1</v>
+        <v>12</v>
       </c>
       <c r="B297">
-        <v>0.13</v>
+        <v>0.205</v>
       </c>
       <c r="C297" t="s">
         <v>5</v>
@@ -4540,10 +4540,10 @@
     </row>
     <row r="298" spans="1:4">
       <c r="A298">
-        <v>14.5</v>
+        <v>18.8</v>
       </c>
       <c r="B298">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C298" t="s">
         <v>5</v>
@@ -4554,10 +4554,10 @@
     </row>
     <row r="299" spans="1:4">
       <c r="A299">
-        <v>14.2</v>
+        <v>18.3</v>
       </c>
       <c r="B299">
-        <v>0.223</v>
+        <v>0.397</v>
       </c>
       <c r="C299" t="s">
         <v>5</v>
@@ -4568,10 +4568,10 @@
     </row>
     <row r="300" spans="1:4">
       <c r="A300">
-        <v>14.9</v>
+        <v>12.4</v>
       </c>
       <c r="B300">
-        <v>0.358</v>
+        <v>0.39</v>
       </c>
       <c r="C300" t="s">
         <v>5</v>
@@ -4582,10 +4582,10 @@
     </row>
     <row r="301" spans="1:4">
       <c r="A301">
-        <v>21.6</v>
+        <v>25</v>
       </c>
       <c r="B301">
-        <v>0.856</v>
+        <v>0.611</v>
       </c>
       <c r="C301" t="s">
         <v>5</v>
@@ -4596,10 +4596,10 @@
     </row>
     <row r="302" spans="1:4">
       <c r="A302">
-        <v>12</v>
+        <v>22.7</v>
       </c>
       <c r="B302">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C302" t="s">
         <v>6</v>
@@ -4610,10 +4610,10 @@
     </row>
     <row r="303" spans="1:4">
       <c r="A303">
-        <v>29.9</v>
+        <v>25.8</v>
       </c>
       <c r="B303">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C303" t="s">
         <v>6</v>
@@ -4624,10 +4624,10 @@
     </row>
     <row r="304" spans="1:4">
       <c r="A304">
-        <v>22.3</v>
+        <v>19.1</v>
       </c>
       <c r="B304">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C304" t="s">
         <v>6</v>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="305" spans="1:4">
       <c r="A305">
-        <v>20.4</v>
+        <v>16.1</v>
       </c>
       <c r="B305">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C305" t="s">
         <v>6</v>
@@ -4652,10 +4652,10 @@
     </row>
     <row r="306" spans="1:4">
       <c r="A306">
-        <v>39.8</v>
+        <v>21.2</v>
       </c>
       <c r="B306">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C306" t="s">
         <v>6</v>
@@ -4669,7 +4669,7 @@
         <v>24</v>
       </c>
       <c r="B307">
-        <v>0.803</v>
+        <v>2.633</v>
       </c>
       <c r="C307" t="s">
         <v>6</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="308" spans="1:4">
       <c r="A308">
-        <v>14.2</v>
+        <v>20.6</v>
       </c>
       <c r="B308">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C308" t="s">
         <v>6</v>
@@ -4694,10 +4694,10 @@
     </row>
     <row r="309" spans="1:4">
       <c r="A309">
-        <v>48.1</v>
+        <v>20.8</v>
       </c>
       <c r="B309">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C309" t="s">
         <v>6</v>
@@ -4708,10 +4708,10 @@
     </row>
     <row r="310" spans="1:4">
       <c r="A310">
-        <v>19.3</v>
+        <v>15.3</v>
       </c>
       <c r="B310">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C310" t="s">
         <v>6</v>
@@ -4722,10 +4722,10 @@
     </row>
     <row r="311" spans="1:4">
       <c r="A311">
-        <v>38.1</v>
+        <v>20.3</v>
       </c>
       <c r="B311">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C311" t="s">
         <v>6</v>
@@ -4736,10 +4736,10 @@
     </row>
     <row r="312" spans="1:4">
       <c r="A312">
-        <v>23.9</v>
+        <v>12.2</v>
       </c>
       <c r="B312">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C312" t="s">
         <v>6</v>
@@ -4750,10 +4750,10 @@
     </row>
     <row r="313" spans="1:4">
       <c r="A313">
-        <v>26</v>
+        <v>13.2</v>
       </c>
       <c r="B313">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C313" t="s">
         <v>6</v>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="314" spans="1:4">
       <c r="A314">
-        <v>26</v>
+        <v>13.3</v>
       </c>
       <c r="B314">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C314" t="s">
         <v>6</v>
@@ -4778,10 +4778,10 @@
     </row>
     <row r="315" spans="1:4">
       <c r="A315">
-        <v>37.7</v>
+        <v>20.1</v>
       </c>
       <c r="B315">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C315" t="s">
         <v>6</v>
@@ -4792,10 +4792,10 @@
     </row>
     <row r="316" spans="1:4">
       <c r="A316">
-        <v>15.8</v>
+        <v>22.9</v>
       </c>
       <c r="B316">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C316" t="s">
         <v>6</v>
@@ -4806,10 +4806,10 @@
     </row>
     <row r="317" spans="1:4">
       <c r="A317">
-        <v>22.6</v>
+        <v>17.8</v>
       </c>
       <c r="B317">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C317" t="s">
         <v>6</v>
@@ -4820,10 +4820,10 @@
     </row>
     <row r="318" spans="1:4">
       <c r="A318">
-        <v>16</v>
+        <v>23.1</v>
       </c>
       <c r="B318">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C318" t="s">
         <v>6</v>
@@ -4834,10 +4834,10 @@
     </row>
     <row r="319" spans="1:4">
       <c r="A319">
-        <v>31.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="B319">
-        <v>3.24</v>
+        <v>0.86</v>
       </c>
       <c r="C319" t="s">
         <v>6</v>
@@ -4848,10 +4848,10 @@
     </row>
     <row r="320" spans="1:4">
       <c r="A320">
-        <v>23</v>
+        <v>18.1</v>
       </c>
       <c r="B320">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C320" t="s">
         <v>6</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="321" spans="1:4">
       <c r="A321">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="B321">
-        <v>2.138</v>
+        <v>1.733</v>
       </c>
       <c r="C321" t="s">
         <v>6</v>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="322" spans="1:4">
       <c r="A322">
-        <v>38.8</v>
+        <v>20.7</v>
       </c>
       <c r="B322">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C322" t="s">
         <v>6</v>
@@ -4890,10 +4890,10 @@
     </row>
     <row r="323" spans="1:4">
       <c r="A323">
-        <v>19</v>
+        <v>21.7</v>
       </c>
       <c r="B323">
-        <v>1.916</v>
+        <v>2.128</v>
       </c>
       <c r="C323" t="s">
         <v>6</v>
@@ -4904,10 +4904,10 @@
     </row>
     <row r="324" spans="1:4">
       <c r="A324">
-        <v>40.7</v>
+        <v>21.7</v>
       </c>
       <c r="B324">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C324" t="s">
         <v>6</v>
@@ -4918,10 +4918,10 @@
     </row>
     <row r="325" spans="1:4">
       <c r="A325">
-        <v>43.8</v>
+        <v>18.9</v>
       </c>
       <c r="B325">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C325" t="s">
         <v>6</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="326" spans="1:4">
       <c r="A326">
-        <v>11</v>
+        <v>20.7</v>
       </c>
       <c r="B326">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C326" t="s">
         <v>6</v>
@@ -4946,10 +4946,10 @@
     </row>
     <row r="327" spans="1:4">
       <c r="A327">
-        <v>38.4</v>
+        <v>26.6</v>
       </c>
       <c r="B327">
-        <v>4.446</v>
+        <v>2.032</v>
       </c>
       <c r="C327" t="s">
         <v>6</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="328" spans="1:4">
       <c r="A328">
-        <v>48.1</v>
+        <v>20.8</v>
       </c>
       <c r="B328">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C328" t="s">
         <v>6</v>
@@ -4974,10 +4974,10 @@
     </row>
     <row r="329" spans="1:4">
       <c r="A329">
-        <v>27.8</v>
+        <v>38</v>
       </c>
       <c r="B329">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C329" t="s">
         <v>6</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="330" spans="1:4">
       <c r="A330">
-        <v>17.4</v>
+        <v>26.8</v>
       </c>
       <c r="B330">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C330" t="s">
         <v>6</v>
@@ -5002,10 +5002,10 @@
     </row>
     <row r="331" spans="1:4">
       <c r="A331">
-        <v>24.3</v>
+        <v>19.2</v>
       </c>
       <c r="B331">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C331" t="s">
         <v>6</v>
@@ -5016,10 +5016,10 @@
     </row>
     <row r="332" spans="1:4">
       <c r="A332">
-        <v>26.3</v>
+        <v>22.7</v>
       </c>
       <c r="B332">
-        <v>1.311</v>
+        <v>1.849</v>
       </c>
       <c r="C332" t="s">
         <v>6</v>
@@ -5030,10 +5030,10 @@
     </row>
     <row r="333" spans="1:4">
       <c r="A333">
-        <v>20.5</v>
+        <v>16.1</v>
       </c>
       <c r="B333">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C333" t="s">
         <v>6</v>
@@ -5044,10 +5044,10 @@
     </row>
     <row r="334" spans="1:4">
       <c r="A334">
-        <v>16.3</v>
+        <v>25.2</v>
       </c>
       <c r="B334">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C334" t="s">
         <v>6</v>
@@ -5058,10 +5058,10 @@
     </row>
     <row r="335" spans="1:4">
       <c r="A335">
-        <v>29.1</v>
+        <v>25.2</v>
       </c>
       <c r="B335">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C335" t="s">
         <v>6</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="336" spans="1:4">
       <c r="A336">
-        <v>29.5</v>
+        <v>12.2</v>
       </c>
       <c r="B336">
-        <v>1.959</v>
+        <v>1.142</v>
       </c>
       <c r="C336" t="s">
         <v>6</v>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="337" spans="1:4">
       <c r="A337">
-        <v>21.7</v>
+        <v>17.1</v>
       </c>
       <c r="B337">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C337" t="s">
         <v>6</v>
@@ -5100,10 +5100,10 @@
     </row>
     <row r="338" spans="1:4">
       <c r="A338">
-        <v>24.3</v>
+        <v>20.9</v>
       </c>
       <c r="B338">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C338" t="s">
         <v>6</v>
@@ -5114,10 +5114,10 @@
     </row>
     <row r="339" spans="1:4">
       <c r="A339">
-        <v>27.2</v>
+        <v>23.5</v>
       </c>
       <c r="B339">
-        <v>1.311</v>
+        <v>1.849</v>
       </c>
       <c r="C339" t="s">
         <v>6</v>
@@ -5128,10 +5128,10 @@
     </row>
     <row r="340" spans="1:4">
       <c r="A340">
-        <v>28.2</v>
+        <v>11.7</v>
       </c>
       <c r="B340">
-        <v>1.959</v>
+        <v>1.142</v>
       </c>
       <c r="C340" t="s">
         <v>6</v>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="341" spans="1:4">
       <c r="A341">
-        <v>41.6</v>
+        <v>22.2</v>
       </c>
       <c r="B341">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C341" t="s">
         <v>6</v>
@@ -5156,10 +5156,10 @@
     </row>
     <row r="342" spans="1:4">
       <c r="A342">
-        <v>17.1</v>
+        <v>24.8</v>
       </c>
       <c r="B342">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C342" t="s">
         <v>6</v>
@@ -5170,10 +5170,10 @@
     </row>
     <row r="343" spans="1:4">
       <c r="A343">
-        <v>23.1</v>
+        <v>19.9</v>
       </c>
       <c r="B343">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C343" t="s">
         <v>6</v>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="344" spans="1:4">
       <c r="A344">
-        <v>14.6</v>
+        <v>21.1</v>
       </c>
       <c r="B344">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C344" t="s">
         <v>6</v>
@@ -5198,10 +5198,10 @@
     </row>
     <row r="345" spans="1:4">
       <c r="A345">
-        <v>26.1</v>
+        <v>12.5</v>
       </c>
       <c r="B345">
-        <v>2.367</v>
+        <v>0.704</v>
       </c>
       <c r="C345" t="s">
         <v>6</v>
@@ -5212,10 +5212,10 @@
     </row>
     <row r="346" spans="1:4">
       <c r="A346">
-        <v>27.9</v>
+        <v>11.5</v>
       </c>
       <c r="B346">
-        <v>1.959</v>
+        <v>1.142</v>
       </c>
       <c r="C346" t="s">
         <v>6</v>
@@ -5226,10 +5226,10 @@
     </row>
     <row r="347" spans="1:4">
       <c r="A347">
-        <v>12.1</v>
+        <v>22.8</v>
       </c>
       <c r="B347">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C347" t="s">
         <v>6</v>
@@ -5240,10 +5240,10 @@
     </row>
     <row r="348" spans="1:4">
       <c r="A348">
-        <v>14.8</v>
+        <v>21.4</v>
       </c>
       <c r="B348">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C348" t="s">
         <v>6</v>
@@ -5254,10 +5254,10 @@
     </row>
     <row r="349" spans="1:4">
       <c r="A349">
-        <v>23.2</v>
+        <v>22.1</v>
       </c>
       <c r="B349">
-        <v>2.138</v>
+        <v>1.733</v>
       </c>
       <c r="C349" t="s">
         <v>6</v>
@@ -5268,10 +5268,10 @@
     </row>
     <row r="350" spans="1:4">
       <c r="A350">
-        <v>33.1</v>
+        <v>10.9</v>
       </c>
       <c r="B350">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C350" t="s">
         <v>6</v>
@@ -5282,10 +5282,10 @@
     </row>
     <row r="351" spans="1:4">
       <c r="A351">
-        <v>28.1</v>
+        <v>14.3</v>
       </c>
       <c r="B351">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C351" t="s">
         <v>6</v>
@@ -5299,7 +5299,7 @@
         <v>25.2</v>
       </c>
       <c r="B352">
-        <v>0.803</v>
+        <v>2.633</v>
       </c>
       <c r="C352" t="s">
         <v>6</v>
@@ -5310,10 +5310,10 @@
     </row>
     <row r="353" spans="1:4">
       <c r="A353">
-        <v>25.6</v>
+        <v>12.2</v>
       </c>
       <c r="B353">
-        <v>2.367</v>
+        <v>0.704</v>
       </c>
       <c r="C353" t="s">
         <v>6</v>
@@ -5324,10 +5324,10 @@
     </row>
     <row r="354" spans="1:4">
       <c r="A354">
-        <v>23.2</v>
+        <v>11.8</v>
       </c>
       <c r="B354">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C354" t="s">
         <v>6</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="355" spans="1:4">
       <c r="A355">
-        <v>22.9</v>
+        <v>11.7</v>
       </c>
       <c r="B355">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C355" t="s">
         <v>6</v>
@@ -5352,10 +5352,10 @@
     </row>
     <row r="356" spans="1:4">
       <c r="A356">
-        <v>15.4</v>
+        <v>22.3</v>
       </c>
       <c r="B356">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C356" t="s">
         <v>6</v>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="357" spans="1:4">
       <c r="A357">
-        <v>21.6</v>
+        <v>20.5</v>
       </c>
       <c r="B357">
-        <v>2.138</v>
+        <v>1.733</v>
       </c>
       <c r="C357" t="s">
         <v>6</v>
@@ -5380,10 +5380,10 @@
     </row>
     <row r="358" spans="1:4">
       <c r="A358">
-        <v>28.4</v>
+        <v>24.6</v>
       </c>
       <c r="B358">
-        <v>1.311</v>
+        <v>1.849</v>
       </c>
       <c r="C358" t="s">
         <v>6</v>
@@ -5397,7 +5397,7 @@
         <v>26.7</v>
       </c>
       <c r="B359">
-        <v>0.803</v>
+        <v>2.633</v>
       </c>
       <c r="C359" t="s">
         <v>6</v>
@@ -5408,10 +5408,10 @@
     </row>
     <row r="360" spans="1:4">
       <c r="A360">
-        <v>10.7</v>
+        <v>20.1</v>
       </c>
       <c r="B360">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C360" t="s">
         <v>6</v>
@@ -5422,10 +5422,10 @@
     </row>
     <row r="361" spans="1:4">
       <c r="A361">
-        <v>15.4</v>
+        <v>23.9</v>
       </c>
       <c r="B361">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C361" t="s">
         <v>6</v>
@@ -5436,10 +5436,10 @@
     </row>
     <row r="362" spans="1:4">
       <c r="A362">
-        <v>23</v>
+        <v>11.7</v>
       </c>
       <c r="B362">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C362" t="s">
         <v>6</v>
@@ -5453,7 +5453,7 @@
         <v>23.3</v>
       </c>
       <c r="B363">
-        <v>0.803</v>
+        <v>2.633</v>
       </c>
       <c r="C363" t="s">
         <v>6</v>
@@ -5464,10 +5464,10 @@
     </row>
     <row r="364" spans="1:4">
       <c r="A364">
-        <v>48.7</v>
+        <v>21.1</v>
       </c>
       <c r="B364">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C364" t="s">
         <v>6</v>
@@ -5478,10 +5478,10 @@
     </row>
     <row r="365" spans="1:4">
       <c r="A365">
-        <v>36.8</v>
+        <v>12.1</v>
       </c>
       <c r="B365">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C365" t="s">
         <v>6</v>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="366" spans="1:4">
       <c r="A366">
-        <v>21.7</v>
+        <v>18.6</v>
       </c>
       <c r="B366">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C366" t="s">
         <v>6</v>
@@ -5506,10 +5506,10 @@
     </row>
     <row r="367" spans="1:4">
       <c r="A367">
-        <v>43.7</v>
+        <v>18.8</v>
       </c>
       <c r="B367">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C367" t="s">
         <v>6</v>
@@ -5520,10 +5520,10 @@
     </row>
     <row r="368" spans="1:4">
       <c r="A368">
-        <v>26.5</v>
+        <v>36.3</v>
       </c>
       <c r="B368">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C368" t="s">
         <v>6</v>
@@ -5534,10 +5534,10 @@
     </row>
     <row r="369" spans="1:4">
       <c r="A369">
-        <v>25</v>
+        <v>10.3</v>
       </c>
       <c r="B369">
-        <v>1.959</v>
+        <v>1.142</v>
       </c>
       <c r="C369" t="s">
         <v>6</v>
@@ -5548,10 +5548,10 @@
     </row>
     <row r="370" spans="1:4">
       <c r="A370">
-        <v>48</v>
+        <v>20.7</v>
       </c>
       <c r="B370">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C370" t="s">
         <v>6</v>
@@ -5562,10 +5562,10 @@
     </row>
     <row r="371" spans="1:4">
       <c r="A371">
-        <v>15.4</v>
+        <v>22.3</v>
       </c>
       <c r="B371">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C371" t="s">
         <v>6</v>
@@ -5576,10 +5576,10 @@
     </row>
     <row r="372" spans="1:4">
       <c r="A372">
-        <v>11.4</v>
+        <v>21.5</v>
       </c>
       <c r="B372">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C372" t="s">
         <v>6</v>
@@ -5590,10 +5590,10 @@
     </row>
     <row r="373" spans="1:4">
       <c r="A373">
-        <v>23.4</v>
+        <v>20.1</v>
       </c>
       <c r="B373">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C373" t="s">
         <v>6</v>
@@ -5604,10 +5604,10 @@
     </row>
     <row r="374" spans="1:4">
       <c r="A374">
-        <v>12.4</v>
+        <v>23.3</v>
       </c>
       <c r="B374">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C374" t="s">
         <v>6</v>
@@ -5618,10 +5618,10 @@
     </row>
     <row r="375" spans="1:4">
       <c r="A375">
-        <v>34.8</v>
+        <v>24.1</v>
       </c>
       <c r="B375">
-        <v>4.446</v>
+        <v>2.032</v>
       </c>
       <c r="C375" t="s">
         <v>6</v>
@@ -5632,10 +5632,10 @@
     </row>
     <row r="376" spans="1:4">
       <c r="A376">
-        <v>26.1</v>
+        <v>22.6</v>
       </c>
       <c r="B376">
-        <v>1.311</v>
+        <v>1.849</v>
       </c>
       <c r="C376" t="s">
         <v>6</v>
@@ -5646,10 +5646,10 @@
     </row>
     <row r="377" spans="1:4">
       <c r="A377">
-        <v>24.7</v>
+        <v>12.6</v>
       </c>
       <c r="B377">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C377" t="s">
         <v>6</v>
@@ -5660,10 +5660,10 @@
     </row>
     <row r="378" spans="1:4">
       <c r="A378">
-        <v>38.9</v>
+        <v>12.8</v>
       </c>
       <c r="B378">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C378" t="s">
         <v>6</v>
@@ -5674,10 +5674,10 @@
     </row>
     <row r="379" spans="1:4">
       <c r="A379">
-        <v>15.7</v>
+        <v>24.2</v>
       </c>
       <c r="B379">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C379" t="s">
         <v>6</v>
@@ -5688,10 +5688,10 @@
     </row>
     <row r="380" spans="1:4">
       <c r="A380">
-        <v>35.9</v>
+        <v>24.8</v>
       </c>
       <c r="B380">
-        <v>4.446</v>
+        <v>2.032</v>
       </c>
       <c r="C380" t="s">
         <v>6</v>
@@ -5702,10 +5702,10 @@
     </row>
     <row r="381" spans="1:4">
       <c r="A381">
-        <v>36.7</v>
+        <v>12.1</v>
       </c>
       <c r="B381">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C381" t="s">
         <v>6</v>
@@ -5716,10 +5716,10 @@
     </row>
     <row r="382" spans="1:4">
       <c r="A382">
-        <v>20.5</v>
+        <v>23.5</v>
       </c>
       <c r="B382">
-        <v>1.916</v>
+        <v>2.128</v>
       </c>
       <c r="C382" t="s">
         <v>6</v>
@@ -5730,10 +5730,10 @@
     </row>
     <row r="383" spans="1:4">
       <c r="A383">
-        <v>30.6</v>
+        <v>9.5</v>
       </c>
       <c r="B383">
-        <v>3.24</v>
+        <v>0.86</v>
       </c>
       <c r="C383" t="s">
         <v>6</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="384" spans="1:4">
       <c r="A384">
-        <v>19.5</v>
+        <v>22.2</v>
       </c>
       <c r="B384">
-        <v>1.916</v>
+        <v>2.128</v>
       </c>
       <c r="C384" t="s">
         <v>6</v>
@@ -5758,10 +5758,10 @@
     </row>
     <row r="385" spans="1:4">
       <c r="A385">
-        <v>32.3</v>
+        <v>44.3</v>
       </c>
       <c r="B385">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C385" t="s">
         <v>6</v>
@@ -5772,10 +5772,10 @@
     </row>
     <row r="386" spans="1:4">
       <c r="A386">
-        <v>32.2</v>
+        <v>27.8</v>
       </c>
       <c r="B386">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C386" t="s">
         <v>6</v>
@@ -5789,7 +5789,7 @@
         <v>28.5</v>
       </c>
       <c r="B387">
-        <v>0.803</v>
+        <v>2.633</v>
       </c>
       <c r="C387" t="s">
         <v>6</v>
@@ -5800,10 +5800,10 @@
     </row>
     <row r="388" spans="1:4">
       <c r="A388">
-        <v>29.9</v>
+        <v>25.8</v>
       </c>
       <c r="B388">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C388" t="s">
         <v>6</v>
@@ -5814,10 +5814,10 @@
     </row>
     <row r="389" spans="1:4">
       <c r="A389">
-        <v>16</v>
+        <v>24.7</v>
       </c>
       <c r="B389">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C389" t="s">
         <v>6</v>
@@ -5828,10 +5828,10 @@
     </row>
     <row r="390" spans="1:4">
       <c r="A390">
-        <v>43.7</v>
+        <v>23.3</v>
       </c>
       <c r="B390">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C390" t="s">
         <v>6</v>
@@ -5842,10 +5842,10 @@
     </row>
     <row r="391" spans="1:4">
       <c r="A391">
-        <v>48.8</v>
+        <v>21.1</v>
       </c>
       <c r="B391">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C391" t="s">
         <v>6</v>
@@ -5856,10 +5856,10 @@
     </row>
     <row r="392" spans="1:4">
       <c r="A392">
-        <v>23.4</v>
+        <v>11.9</v>
       </c>
       <c r="B392">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C392" t="s">
         <v>6</v>
@@ -5870,10 +5870,10 @@
     </row>
     <row r="393" spans="1:4">
       <c r="A393">
-        <v>29.5</v>
+        <v>40.5</v>
       </c>
       <c r="B393">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C393" t="s">
         <v>6</v>
@@ -5884,10 +5884,10 @@
     </row>
     <row r="394" spans="1:4">
       <c r="A394">
-        <v>37.6</v>
+        <v>26.1</v>
       </c>
       <c r="B394">
-        <v>4.446</v>
+        <v>2.032</v>
       </c>
       <c r="C394" t="s">
         <v>6</v>
@@ -5898,10 +5898,10 @@
     </row>
     <row r="395" spans="1:4">
       <c r="A395">
-        <v>47</v>
+        <v>20.4</v>
       </c>
       <c r="B395">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C395" t="s">
         <v>6</v>
@@ -5912,10 +5912,10 @@
     </row>
     <row r="396" spans="1:4">
       <c r="A396">
-        <v>30.7</v>
+        <v>9.5</v>
       </c>
       <c r="B396">
-        <v>3.24</v>
+        <v>0.86</v>
       </c>
       <c r="C396" t="s">
         <v>6</v>
@@ -5926,10 +5926,10 @@
     </row>
     <row r="397" spans="1:4">
       <c r="A397">
-        <v>16.5</v>
+        <v>23.8</v>
       </c>
       <c r="B397">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C397" t="s">
         <v>6</v>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="398" spans="1:4">
       <c r="A398">
-        <v>38.6</v>
+        <v>20.6</v>
       </c>
       <c r="B398">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C398" t="s">
         <v>6</v>
@@ -5954,10 +5954,10 @@
     </row>
     <row r="399" spans="1:4">
       <c r="A399">
-        <v>27.1</v>
+        <v>37.1</v>
       </c>
       <c r="B399">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C399" t="s">
         <v>6</v>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="400" spans="1:4">
       <c r="A400">
-        <v>20</v>
+        <v>22.8</v>
       </c>
       <c r="B400">
-        <v>1.916</v>
+        <v>2.128</v>
       </c>
       <c r="C400" t="s">
         <v>6</v>
@@ -5982,10 +5982,10 @@
     </row>
     <row r="401" spans="1:4">
       <c r="A401">
-        <v>46</v>
+        <v>19.8</v>
       </c>
       <c r="B401">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C401" t="s">
         <v>6</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="402" spans="1:4">
       <c r="A402">
-        <v>21.1</v>
+        <v>20.1</v>
       </c>
       <c r="B402">
-        <v>2.138</v>
+        <v>1.733</v>
       </c>
       <c r="C402" t="s">
         <v>6</v>
@@ -6010,10 +6010,10 @@
     </row>
     <row r="403" spans="1:4">
       <c r="A403">
-        <v>23.3</v>
+        <v>20</v>
       </c>
       <c r="B403">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C403" t="s">
         <v>6</v>
@@ -6024,10 +6024,10 @@
     </row>
     <row r="404" spans="1:4">
       <c r="A404">
-        <v>42.1</v>
+        <v>22.4</v>
       </c>
       <c r="B404">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C404" t="s">
         <v>6</v>
@@ -6038,10 +6038,10 @@
     </row>
     <row r="405" spans="1:4">
       <c r="A405">
-        <v>24.1</v>
+        <v>20.7</v>
       </c>
       <c r="B405">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C405" t="s">
         <v>6</v>
@@ -6052,10 +6052,10 @@
     </row>
     <row r="406" spans="1:4">
       <c r="A406">
-        <v>49.3</v>
+        <v>21.3</v>
       </c>
       <c r="B406">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C406" t="s">
         <v>6</v>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="407" spans="1:4">
       <c r="A407">
-        <v>32.7</v>
+        <v>28.3</v>
       </c>
       <c r="B407">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C407" t="s">
         <v>6</v>
@@ -6080,10 +6080,10 @@
     </row>
     <row r="408" spans="1:4">
       <c r="A408">
-        <v>46.4</v>
+        <v>20.1</v>
       </c>
       <c r="B408">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C408" t="s">
         <v>6</v>
@@ -6094,10 +6094,10 @@
     </row>
     <row r="409" spans="1:4">
       <c r="A409">
-        <v>32.9</v>
+        <v>10.2</v>
       </c>
       <c r="B409">
-        <v>3.24</v>
+        <v>0.86</v>
       </c>
       <c r="C409" t="s">
         <v>6</v>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="410" spans="1:4">
       <c r="A410">
-        <v>14.7</v>
+        <v>21.3</v>
       </c>
       <c r="B410">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C410" t="s">
         <v>6</v>
@@ -6122,10 +6122,10 @@
     </row>
     <row r="411" spans="1:4">
       <c r="A411">
-        <v>24.9</v>
+        <v>11.9</v>
       </c>
       <c r="B411">
-        <v>2.367</v>
+        <v>0.704</v>
       </c>
       <c r="C411" t="s">
         <v>6</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="412" spans="1:4">
       <c r="A412">
-        <v>24.8</v>
+        <v>12.7</v>
       </c>
       <c r="B412">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C412" t="s">
         <v>6</v>
@@ -6150,10 +6150,10 @@
     </row>
     <row r="413" spans="1:4">
       <c r="A413">
-        <v>26</v>
+        <v>10.8</v>
       </c>
       <c r="B413">
-        <v>1.959</v>
+        <v>1.142</v>
       </c>
       <c r="C413" t="s">
         <v>6</v>
@@ -6164,10 +6164,10 @@
     </row>
     <row r="414" spans="1:4">
       <c r="A414">
-        <v>33</v>
+        <v>28.5</v>
       </c>
       <c r="B414">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C414" t="s">
         <v>6</v>
@@ -6178,10 +6178,10 @@
     </row>
     <row r="415" spans="1:4">
       <c r="A415">
-        <v>30.2</v>
+        <v>41.3</v>
       </c>
       <c r="B415">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C415" t="s">
         <v>6</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="416" spans="1:4">
       <c r="A416">
-        <v>46.6</v>
+        <v>20.1</v>
       </c>
       <c r="B416">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C416" t="s">
         <v>6</v>
@@ -6206,10 +6206,10 @@
     </row>
     <row r="417" spans="1:4">
       <c r="A417">
-        <v>34.4</v>
+        <v>11.3</v>
       </c>
       <c r="B417">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C417" t="s">
         <v>6</v>
@@ -6220,10 +6220,10 @@
     </row>
     <row r="418" spans="1:4">
       <c r="A418">
-        <v>35.6</v>
+        <v>11.7</v>
       </c>
       <c r="B418">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C418" t="s">
         <v>6</v>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="419" spans="1:4">
       <c r="A419">
-        <v>25.6</v>
+        <v>12.2</v>
       </c>
       <c r="B419">
-        <v>2.367</v>
+        <v>0.704</v>
       </c>
       <c r="C419" t="s">
         <v>6</v>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="420" spans="1:4">
       <c r="A420">
-        <v>22.9</v>
+        <v>19.7</v>
       </c>
       <c r="B420">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C420" t="s">
         <v>6</v>
@@ -6262,10 +6262,10 @@
     </row>
     <row r="421" spans="1:4">
       <c r="A421">
-        <v>30</v>
+        <v>25.9</v>
       </c>
       <c r="B421">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C421" t="s">
         <v>6</v>
@@ -6276,10 +6276,10 @@
     </row>
     <row r="422" spans="1:4">
       <c r="A422">
-        <v>49.4</v>
+        <v>21.4</v>
       </c>
       <c r="B422">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C422" t="s">
         <v>6</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="423" spans="1:4">
       <c r="A423">
-        <v>49.5</v>
+        <v>21.4</v>
       </c>
       <c r="B423">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C423" t="s">
         <v>6</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="424" spans="1:4">
       <c r="A424">
-        <v>12.1</v>
+        <v>22.7</v>
       </c>
       <c r="B424">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C424" t="s">
         <v>6</v>
@@ -6318,10 +6318,10 @@
     </row>
     <row r="425" spans="1:4">
       <c r="A425">
-        <v>20.7</v>
+        <v>16.3</v>
       </c>
       <c r="B425">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C425" t="s">
         <v>6</v>
@@ -6332,10 +6332,10 @@
     </row>
     <row r="426" spans="1:4">
       <c r="A426">
-        <v>29.3</v>
+        <v>40.2</v>
       </c>
       <c r="B426">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C426" t="s">
         <v>6</v>
@@ -6346,10 +6346,10 @@
     </row>
     <row r="427" spans="1:4">
       <c r="A427">
-        <v>45.8</v>
+        <v>19.8</v>
       </c>
       <c r="B427">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C427" t="s">
         <v>6</v>
@@ -6360,10 +6360,10 @@
     </row>
     <row r="428" spans="1:4">
       <c r="A428">
-        <v>16.9</v>
+        <v>24.4</v>
       </c>
       <c r="B428">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C428" t="s">
         <v>6</v>
@@ -6374,10 +6374,10 @@
     </row>
     <row r="429" spans="1:4">
       <c r="A429">
-        <v>40.3</v>
+        <v>21.5</v>
       </c>
       <c r="B429">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C429" t="s">
         <v>6</v>
@@ -6388,10 +6388,10 @@
     </row>
     <row r="430" spans="1:4">
       <c r="A430">
-        <v>27.9</v>
+        <v>38.2</v>
       </c>
       <c r="B430">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C430" t="s">
         <v>6</v>
@@ -6402,10 +6402,10 @@
     </row>
     <row r="431" spans="1:4">
       <c r="A431">
-        <v>41.4</v>
+        <v>22.1</v>
       </c>
       <c r="B431">
-        <v>6.584</v>
+        <v>3.181</v>
       </c>
       <c r="C431" t="s">
         <v>6</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="432" spans="1:4">
       <c r="A432">
-        <v>24.5</v>
+        <v>21.1</v>
       </c>
       <c r="B432">
-        <v>3.592</v>
+        <v>1.388</v>
       </c>
       <c r="C432" t="s">
         <v>6</v>
@@ -6430,10 +6430,10 @@
     </row>
     <row r="433" spans="1:4">
       <c r="A433">
-        <v>25.5</v>
+        <v>13</v>
       </c>
       <c r="B433">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C433" t="s">
         <v>6</v>
@@ -6444,10 +6444,10 @@
     </row>
     <row r="434" spans="1:4">
       <c r="A434">
-        <v>29.5</v>
+        <v>40.4</v>
       </c>
       <c r="B434">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C434" t="s">
         <v>6</v>
@@ -6458,10 +6458,10 @@
     </row>
     <row r="435" spans="1:4">
       <c r="A435">
-        <v>12.4</v>
+        <v>23.4</v>
       </c>
       <c r="B435">
-        <v>0.428</v>
+        <v>1.059</v>
       </c>
       <c r="C435" t="s">
         <v>6</v>
@@ -6472,10 +6472,10 @@
     </row>
     <row r="436" spans="1:4">
       <c r="A436">
-        <v>32</v>
+        <v>27.6</v>
       </c>
       <c r="B436">
-        <v>4.263</v>
+        <v>2.241</v>
       </c>
       <c r="C436" t="s">
         <v>6</v>
@@ -6486,10 +6486,10 @@
     </row>
     <row r="437" spans="1:4">
       <c r="A437">
-        <v>28.3</v>
+        <v>38.8</v>
       </c>
       <c r="B437">
-        <v>2.258</v>
+        <v>3.719</v>
       </c>
       <c r="C437" t="s">
         <v>6</v>
@@ -6500,10 +6500,10 @@
     </row>
     <row r="438" spans="1:4">
       <c r="A438">
-        <v>44.6</v>
+        <v>19.2</v>
       </c>
       <c r="B438">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C438" t="s">
         <v>6</v>
@@ -6514,10 +6514,10 @@
     </row>
     <row r="439" spans="1:4">
       <c r="A439">
-        <v>19.1</v>
+        <v>21.8</v>
       </c>
       <c r="B439">
-        <v>1.916</v>
+        <v>2.128</v>
       </c>
       <c r="C439" t="s">
         <v>6</v>
@@ -6528,10 +6528,10 @@
     </row>
     <row r="440" spans="1:4">
       <c r="A440">
-        <v>36.9</v>
+        <v>12.1</v>
       </c>
       <c r="B440">
-        <v>5.684</v>
+        <v>0.206</v>
       </c>
       <c r="C440" t="s">
         <v>6</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="441" spans="1:4">
       <c r="A441">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="B441">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C441" t="s">
         <v>6</v>
@@ -6556,10 +6556,10 @@
     </row>
     <row r="442" spans="1:4">
       <c r="A442">
-        <v>17.3</v>
+        <v>26.7</v>
       </c>
       <c r="B442">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C442" t="s">
         <v>6</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="443" spans="1:4">
       <c r="A443">
-        <v>46.8</v>
+        <v>20.2</v>
       </c>
       <c r="B443">
-        <v>6.524</v>
+        <v>1.345</v>
       </c>
       <c r="C443" t="s">
         <v>6</v>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="444" spans="1:4">
       <c r="A444">
-        <v>32.2</v>
+        <v>27.9</v>
       </c>
       <c r="B444">
-        <v>1.311</v>
+        <v>1.849</v>
       </c>
       <c r="C444" t="s">
         <v>6</v>
@@ -6598,10 +6598,10 @@
     </row>
     <row r="445" spans="1:4">
       <c r="A445">
-        <v>26.7</v>
+        <v>13.6</v>
       </c>
       <c r="B445">
-        <v>3.23</v>
+        <v>0.674</v>
       </c>
       <c r="C445" t="s">
         <v>6</v>
@@ -6612,10 +6612,10 @@
     </row>
     <row r="446" spans="1:4">
       <c r="A446">
-        <v>15.9</v>
+        <v>23</v>
       </c>
       <c r="B446">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C446" t="s">
         <v>6</v>
@@ -6626,10 +6626,10 @@
     </row>
     <row r="447" spans="1:4">
       <c r="A447">
-        <v>15.2</v>
+        <v>22</v>
       </c>
       <c r="B447">
-        <v>0.963</v>
+        <v>2.022</v>
       </c>
       <c r="C447" t="s">
         <v>6</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="448" spans="1:4">
       <c r="A448">
-        <v>16.5</v>
+        <v>25.6</v>
       </c>
       <c r="B448">
-        <v>0.777</v>
+        <v>1.424</v>
       </c>
       <c r="C448" t="s">
         <v>6</v>
@@ -6654,10 +6654,10 @@
     </row>
     <row r="449" spans="1:4">
       <c r="A449">
-        <v>21</v>
+        <v>16.5</v>
       </c>
       <c r="B449">
-        <v>0.983</v>
+        <v>0.91</v>
       </c>
       <c r="C449" t="s">
         <v>6</v>
@@ -6668,10 +6668,10 @@
     </row>
     <row r="450" spans="1:4">
       <c r="A450">
-        <v>47.1</v>
+        <v>20.4</v>
       </c>
       <c r="B450">
-        <v>6.939</v>
+        <v>3.433</v>
       </c>
       <c r="C450" t="s">
         <v>6</v>
@@ -6682,10 +6682,10 @@
     </row>
     <row r="451" spans="1:4">
       <c r="A451">
-        <v>23</v>
+        <v>21.9</v>
       </c>
       <c r="B451">
-        <v>2.138</v>
+        <v>1.733</v>
       </c>
       <c r="C451" t="s">
         <v>6</v>
@@ -6696,10 +6696,10 @@
     </row>
     <row r="452" spans="1:4">
       <c r="A452">
-        <v>38.2</v>
+        <v>16.4</v>
       </c>
       <c r="B452">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C452" t="s">
         <v>4</v>
@@ -6710,10 +6710,10 @@
     </row>
     <row r="453" spans="1:4">
       <c r="A453">
-        <v>32.3</v>
+        <v>9.9</v>
       </c>
       <c r="B453">
-        <v>0.469</v>
+        <v>0.051</v>
       </c>
       <c r="C453" t="s">
         <v>4</v>
@@ -6724,10 +6724,10 @@
     </row>
     <row r="454" spans="1:4">
       <c r="A454">
-        <v>20.4</v>
+        <v>18.9</v>
       </c>
       <c r="B454">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C454" t="s">
         <v>4</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="455" spans="1:4">
       <c r="A455">
-        <v>10.4</v>
+        <v>23.1</v>
       </c>
       <c r="B455">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C455" t="s">
         <v>4</v>
@@ -6752,10 +6752,10 @@
     </row>
     <row r="456" spans="1:4">
       <c r="A456">
-        <v>46.7</v>
+        <v>19.4</v>
       </c>
       <c r="B456">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C456" t="s">
         <v>4</v>
@@ -6766,10 +6766,10 @@
     </row>
     <row r="457" spans="1:4">
       <c r="A457">
-        <v>53.6</v>
+        <v>6.7</v>
       </c>
       <c r="B457">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="C457" t="s">
         <v>4</v>
@@ -6780,10 +6780,10 @@
     </row>
     <row r="458" spans="1:4">
       <c r="A458">
-        <v>41.2</v>
+        <v>28.1</v>
       </c>
       <c r="B458">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C458" t="s">
         <v>4</v>
@@ -6794,10 +6794,10 @@
     </row>
     <row r="459" spans="1:4">
       <c r="A459">
-        <v>45.3</v>
+        <v>18.8</v>
       </c>
       <c r="B459">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C459" t="s">
         <v>4</v>
@@ -6808,10 +6808,10 @@
     </row>
     <row r="460" spans="1:4">
       <c r="A460">
-        <v>9.199999999999999</v>
+        <v>20.5</v>
       </c>
       <c r="B460">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C460" t="s">
         <v>4</v>
@@ -6822,10 +6822,10 @@
     </row>
     <row r="461" spans="1:4">
       <c r="A461">
-        <v>54.6</v>
+        <v>22.4</v>
       </c>
       <c r="B461">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C461" t="s">
         <v>4</v>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="462" spans="1:4">
       <c r="A462">
-        <v>45.4</v>
+        <v>18.9</v>
       </c>
       <c r="B462">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C462" t="s">
         <v>4</v>
@@ -6850,10 +6850,10 @@
     </row>
     <row r="463" spans="1:4">
       <c r="A463">
-        <v>60.7</v>
+        <v>7.6</v>
       </c>
       <c r="B463">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="C463" t="s">
         <v>4</v>
@@ -6864,10 +6864,10 @@
     </row>
     <row r="464" spans="1:4">
       <c r="A464">
-        <v>28.2</v>
+        <v>14.7</v>
       </c>
       <c r="B464">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C464" t="s">
         <v>4</v>
@@ -6878,10 +6878,10 @@
     </row>
     <row r="465" spans="1:4">
       <c r="A465">
-        <v>14.4</v>
+        <v>21.8</v>
       </c>
       <c r="B465">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="C465" t="s">
         <v>4</v>
@@ -6892,10 +6892,10 @@
     </row>
     <row r="466" spans="1:4">
       <c r="A466">
-        <v>19.4</v>
+        <v>10.2</v>
       </c>
       <c r="B466">
-        <v>0.061</v>
+        <v>0.042</v>
       </c>
       <c r="C466" t="s">
         <v>4</v>
@@ -6906,10 +6906,10 @@
     </row>
     <row r="467" spans="1:4">
       <c r="A467">
-        <v>36.2</v>
+        <v>19.1</v>
       </c>
       <c r="B467">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C467" t="s">
         <v>4</v>
@@ -6920,10 +6920,10 @@
     </row>
     <row r="468" spans="1:4">
       <c r="A468">
-        <v>8.9</v>
+        <v>26.5</v>
       </c>
       <c r="B468">
-        <v>0.036</v>
+        <v>0.197</v>
       </c>
       <c r="C468" t="s">
         <v>4</v>
@@ -6934,10 +6934,10 @@
     </row>
     <row r="469" spans="1:4">
       <c r="A469">
-        <v>8.800000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="B469">
-        <v>0.036</v>
+        <v>0.197</v>
       </c>
       <c r="C469" t="s">
         <v>4</v>
@@ -6948,10 +6948,10 @@
     </row>
     <row r="470" spans="1:4">
       <c r="A470">
-        <v>43</v>
+        <v>18.5</v>
       </c>
       <c r="B470">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C470" t="s">
         <v>4</v>
@@ -6962,10 +6962,10 @@
     </row>
     <row r="471" spans="1:4">
       <c r="A471">
-        <v>39.9</v>
+        <v>27.1</v>
       </c>
       <c r="B471">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C471" t="s">
         <v>4</v>
@@ -6976,10 +6976,10 @@
     </row>
     <row r="472" spans="1:4">
       <c r="A472">
-        <v>13.4</v>
+        <v>20.4</v>
       </c>
       <c r="B472">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="C472" t="s">
         <v>4</v>
@@ -6990,10 +6990,10 @@
     </row>
     <row r="473" spans="1:4">
       <c r="A473">
-        <v>10.8</v>
+        <v>24</v>
       </c>
       <c r="B473">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C473" t="s">
         <v>4</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="474" spans="1:4">
       <c r="A474">
-        <v>34.9</v>
+        <v>18.4</v>
       </c>
       <c r="B474">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C474" t="s">
         <v>4</v>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="475" spans="1:4">
       <c r="A475">
-        <v>44</v>
+        <v>18.9</v>
       </c>
       <c r="B475">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C475" t="s">
         <v>4</v>
@@ -7032,10 +7032,10 @@
     </row>
     <row r="476" spans="1:4">
       <c r="A476">
-        <v>37.9</v>
+        <v>14.9</v>
       </c>
       <c r="B476">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C476" t="s">
         <v>4</v>
@@ -7046,10 +7046,10 @@
     </row>
     <row r="477" spans="1:4">
       <c r="A477">
-        <v>8.800000000000001</v>
+        <v>26.2</v>
       </c>
       <c r="B477">
-        <v>0.036</v>
+        <v>0.197</v>
       </c>
       <c r="C477" t="s">
         <v>4</v>
@@ -7060,10 +7060,10 @@
     </row>
     <row r="478" spans="1:4">
       <c r="A478">
-        <v>64.40000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="B478">
-        <v>2.037</v>
+        <v>0.056</v>
       </c>
       <c r="C478" t="s">
         <v>4</v>
@@ -7074,10 +7074,10 @@
     </row>
     <row r="479" spans="1:4">
       <c r="A479">
-        <v>36.9</v>
+        <v>19.5</v>
       </c>
       <c r="B479">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C479" t="s">
         <v>4</v>
@@ -7088,10 +7088,10 @@
     </row>
     <row r="480" spans="1:4">
       <c r="A480">
-        <v>45.5</v>
+        <v>18.9</v>
       </c>
       <c r="B480">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C480" t="s">
         <v>4</v>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="481" spans="1:4">
       <c r="A481">
-        <v>16.9</v>
+        <v>25.2</v>
       </c>
       <c r="B481">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C481" t="s">
         <v>4</v>
@@ -7116,10 +7116,10 @@
     </row>
     <row r="482" spans="1:4">
       <c r="A482">
-        <v>45.5</v>
+        <v>14.1</v>
       </c>
       <c r="B482">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C482" t="s">
         <v>4</v>
@@ -7130,10 +7130,10 @@
     </row>
     <row r="483" spans="1:4">
       <c r="A483">
-        <v>20.7</v>
+        <v>10.8</v>
       </c>
       <c r="B483">
-        <v>0.061</v>
+        <v>0.042</v>
       </c>
       <c r="C483" t="s">
         <v>4</v>
@@ -7144,10 +7144,10 @@
     </row>
     <row r="484" spans="1:4">
       <c r="A484">
-        <v>41.2</v>
+        <v>17.7</v>
       </c>
       <c r="B484">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C484" t="s">
         <v>4</v>
@@ -7158,10 +7158,10 @@
     </row>
     <row r="485" spans="1:4">
       <c r="A485">
-        <v>52.9</v>
+        <v>21.7</v>
       </c>
       <c r="B485">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C485" t="s">
         <v>4</v>
@@ -7172,10 +7172,10 @@
     </row>
     <row r="486" spans="1:4">
       <c r="A486">
-        <v>19.2</v>
+        <v>13.3</v>
       </c>
       <c r="B486">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C486" t="s">
         <v>4</v>
@@ -7186,10 +7186,10 @@
     </row>
     <row r="487" spans="1:4">
       <c r="A487">
-        <v>38</v>
+        <v>25.9</v>
       </c>
       <c r="B487">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C487" t="s">
         <v>4</v>
@@ -7200,10 +7200,10 @@
     </row>
     <row r="488" spans="1:4">
       <c r="A488">
-        <v>14.3</v>
+        <v>21.8</v>
       </c>
       <c r="B488">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="C488" t="s">
         <v>4</v>
@@ -7214,10 +7214,10 @@
     </row>
     <row r="489" spans="1:4">
       <c r="A489">
-        <v>39.7</v>
+        <v>17.1</v>
       </c>
       <c r="B489">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C489" t="s">
         <v>4</v>
@@ -7228,10 +7228,10 @@
     </row>
     <row r="490" spans="1:4">
       <c r="A490">
-        <v>53.2</v>
+        <v>21.8</v>
       </c>
       <c r="B490">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C490" t="s">
         <v>4</v>
@@ -7242,10 +7242,10 @@
     </row>
     <row r="491" spans="1:4">
       <c r="A491">
-        <v>33.2</v>
+        <v>10.2</v>
       </c>
       <c r="B491">
-        <v>0.469</v>
+        <v>0.051</v>
       </c>
       <c r="C491" t="s">
         <v>4</v>
@@ -7256,10 +7256,10 @@
     </row>
     <row r="492" spans="1:4">
       <c r="A492">
-        <v>23.8</v>
+        <v>25.8</v>
       </c>
       <c r="B492">
-        <v>0.077</v>
+        <v>0.138</v>
       </c>
       <c r="C492" t="s">
         <v>4</v>
@@ -7270,10 +7270,10 @@
     </row>
     <row r="493" spans="1:4">
       <c r="A493">
-        <v>27.8</v>
+        <v>14.5</v>
       </c>
       <c r="B493">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C493" t="s">
         <v>4</v>
@@ -7284,10 +7284,10 @@
     </row>
     <row r="494" spans="1:4">
       <c r="A494">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="B494">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C494" t="s">
         <v>4</v>
@@ -7298,10 +7298,10 @@
     </row>
     <row r="495" spans="1:4">
       <c r="A495">
-        <v>17.2</v>
+        <v>25.7</v>
       </c>
       <c r="B495">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C495" t="s">
         <v>4</v>
@@ -7312,10 +7312,10 @@
     </row>
     <row r="496" spans="1:4">
       <c r="A496">
-        <v>68.40000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="B496">
-        <v>2.037</v>
+        <v>0.056</v>
       </c>
       <c r="C496" t="s">
         <v>4</v>
@@ -7326,10 +7326,10 @@
     </row>
     <row r="497" spans="1:4">
       <c r="A497">
-        <v>52</v>
+        <v>6.5</v>
       </c>
       <c r="B497">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="C497" t="s">
         <v>4</v>
@@ -7340,10 +7340,10 @@
     </row>
     <row r="498" spans="1:4">
       <c r="A498">
-        <v>19.9</v>
+        <v>10.4</v>
       </c>
       <c r="B498">
-        <v>0.061</v>
+        <v>0.042</v>
       </c>
       <c r="C498" t="s">
         <v>4</v>
@@ -7354,10 +7354,10 @@
     </row>
     <row r="499" spans="1:4">
       <c r="A499">
-        <v>10.4</v>
+        <v>23</v>
       </c>
       <c r="B499">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C499" t="s">
         <v>4</v>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="500" spans="1:4">
       <c r="A500">
-        <v>39.2</v>
+        <v>26.7</v>
       </c>
       <c r="B500">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C500" t="s">
         <v>4</v>
@@ -7382,10 +7382,10 @@
     </row>
     <row r="501" spans="1:4">
       <c r="A501">
-        <v>57.7</v>
+        <v>7.2</v>
       </c>
       <c r="B501">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="C501" t="s">
         <v>4</v>
@@ -7396,10 +7396,10 @@
     </row>
     <row r="502" spans="1:4">
       <c r="A502">
-        <v>11.1</v>
+        <v>24.6</v>
       </c>
       <c r="B502">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C502" t="s">
         <v>4</v>
@@ -7410,10 +7410,10 @@
     </row>
     <row r="503" spans="1:4">
       <c r="A503">
-        <v>20.1</v>
+        <v>10.5</v>
       </c>
       <c r="B503">
-        <v>0.061</v>
+        <v>0.042</v>
       </c>
       <c r="C503" t="s">
         <v>4</v>
@@ -7424,10 +7424,10 @@
     </row>
     <row r="504" spans="1:4">
       <c r="A504">
-        <v>68.2</v>
+        <v>12.8</v>
       </c>
       <c r="B504">
-        <v>2.037</v>
+        <v>0.056</v>
       </c>
       <c r="C504" t="s">
         <v>4</v>
@@ -7438,10 +7438,10 @@
     </row>
     <row r="505" spans="1:4">
       <c r="A505">
-        <v>38.1</v>
+        <v>20.2</v>
       </c>
       <c r="B505">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C505" t="s">
         <v>4</v>
@@ -7452,10 +7452,10 @@
     </row>
     <row r="506" spans="1:4">
       <c r="A506">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="B506">
-        <v>0.079</v>
+        <v>0.2</v>
       </c>
       <c r="C506" t="s">
         <v>4</v>
@@ -7466,10 +7466,10 @@
     </row>
     <row r="507" spans="1:4">
       <c r="A507">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="B507">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C507" t="s">
         <v>4</v>
@@ -7480,10 +7480,10 @@
     </row>
     <row r="508" spans="1:4">
       <c r="A508">
-        <v>37</v>
+        <v>14.5</v>
       </c>
       <c r="B508">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C508" t="s">
         <v>4</v>
@@ -7494,10 +7494,10 @@
     </row>
     <row r="509" spans="1:4">
       <c r="A509">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="B509">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C509" t="s">
         <v>4</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="510" spans="1:4">
       <c r="A510">
-        <v>19.6</v>
+        <v>21.2</v>
       </c>
       <c r="B510">
-        <v>0.077</v>
+        <v>0.138</v>
       </c>
       <c r="C510" t="s">
         <v>4</v>
@@ -7522,10 +7522,10 @@
     </row>
     <row r="511" spans="1:4">
       <c r="A511">
-        <v>36.3</v>
+        <v>14.3</v>
       </c>
       <c r="B511">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C511" t="s">
         <v>4</v>
@@ -7536,10 +7536,10 @@
     </row>
     <row r="512" spans="1:4">
       <c r="A512">
-        <v>17.4</v>
+        <v>25.9</v>
       </c>
       <c r="B512">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C512" t="s">
         <v>4</v>
@@ -7550,10 +7550,10 @@
     </row>
     <row r="513" spans="1:4">
       <c r="A513">
-        <v>21.6</v>
+        <v>23.4</v>
       </c>
       <c r="B513">
-        <v>0.077</v>
+        <v>0.138</v>
       </c>
       <c r="C513" t="s">
         <v>4</v>
@@ -7564,10 +7564,10 @@
     </row>
     <row r="514" spans="1:4">
       <c r="A514">
-        <v>40</v>
+        <v>17.2</v>
       </c>
       <c r="B514">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C514" t="s">
         <v>4</v>
@@ -7578,10 +7578,10 @@
     </row>
     <row r="515" spans="1:4">
       <c r="A515">
-        <v>8.300000000000001</v>
+        <v>24.7</v>
       </c>
       <c r="B515">
-        <v>0.036</v>
+        <v>0.197</v>
       </c>
       <c r="C515" t="s">
         <v>4</v>
@@ -7592,10 +7592,10 @@
     </row>
     <row r="516" spans="1:4">
       <c r="A516">
-        <v>21.6</v>
+        <v>20</v>
       </c>
       <c r="B516">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C516" t="s">
         <v>4</v>
@@ -7606,10 +7606,10 @@
     </row>
     <row r="517" spans="1:4">
       <c r="A517">
-        <v>9.6</v>
+        <v>21.4</v>
       </c>
       <c r="B517">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C517" t="s">
         <v>4</v>
@@ -7620,10 +7620,10 @@
     </row>
     <row r="518" spans="1:4">
       <c r="A518">
-        <v>20.4</v>
+        <v>10.7</v>
       </c>
       <c r="B518">
-        <v>0.061</v>
+        <v>0.042</v>
       </c>
       <c r="C518" t="s">
         <v>4</v>
@@ -7634,10 +7634,10 @@
     </row>
     <row r="519" spans="1:4">
       <c r="A519">
-        <v>49.4</v>
+        <v>20.3</v>
       </c>
       <c r="B519">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C519" t="s">
         <v>4</v>
@@ -7648,10 +7648,10 @@
     </row>
     <row r="520" spans="1:4">
       <c r="A520">
-        <v>23</v>
+        <v>21.3</v>
       </c>
       <c r="B520">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C520" t="s">
         <v>4</v>
@@ -7662,10 +7662,10 @@
     </row>
     <row r="521" spans="1:4">
       <c r="A521">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="B521">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C521" t="s">
         <v>4</v>
@@ -7676,10 +7676,10 @@
     </row>
     <row r="522" spans="1:4">
       <c r="A522">
-        <v>35</v>
+        <v>10.7</v>
       </c>
       <c r="B522">
-        <v>0.469</v>
+        <v>0.051</v>
       </c>
       <c r="C522" t="s">
         <v>4</v>
@@ -7690,10 +7690,10 @@
     </row>
     <row r="523" spans="1:4">
       <c r="A523">
-        <v>19</v>
+        <v>13.2</v>
       </c>
       <c r="B523">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C523" t="s">
         <v>4</v>
@@ -7704,10 +7704,10 @@
     </row>
     <row r="524" spans="1:4">
       <c r="A524">
-        <v>9.800000000000001</v>
+        <v>21.6</v>
       </c>
       <c r="B524">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C524" t="s">
         <v>4</v>
@@ -7718,10 +7718,10 @@
     </row>
     <row r="525" spans="1:4">
       <c r="A525">
-        <v>30.1</v>
+        <v>15.7</v>
       </c>
       <c r="B525">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C525" t="s">
         <v>4</v>
@@ -7732,10 +7732,10 @@
     </row>
     <row r="526" spans="1:4">
       <c r="A526">
-        <v>44</v>
+        <v>18.3</v>
       </c>
       <c r="B526">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C526" t="s">
         <v>4</v>
@@ -7746,10 +7746,10 @@
     </row>
     <row r="527" spans="1:4">
       <c r="A527">
-        <v>17.3</v>
+        <v>25.8</v>
       </c>
       <c r="B527">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C527" t="s">
         <v>4</v>
@@ -7760,10 +7760,10 @@
     </row>
     <row r="528" spans="1:4">
       <c r="A528">
-        <v>32.9</v>
+        <v>12.9</v>
       </c>
       <c r="B528">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C528" t="s">
         <v>4</v>
@@ -7774,10 +7774,10 @@
     </row>
     <row r="529" spans="1:4">
       <c r="A529">
-        <v>38.4</v>
+        <v>26.1</v>
       </c>
       <c r="B529">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C529" t="s">
         <v>4</v>
@@ -7788,10 +7788,10 @@
     </row>
     <row r="530" spans="1:4">
       <c r="A530">
-        <v>16.7</v>
+        <v>24.8</v>
       </c>
       <c r="B530">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C530" t="s">
         <v>4</v>
@@ -7802,10 +7802,10 @@
     </row>
     <row r="531" spans="1:4">
       <c r="A531">
-        <v>45.1</v>
+        <v>14</v>
       </c>
       <c r="B531">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C531" t="s">
         <v>4</v>
@@ -7816,10 +7816,10 @@
     </row>
     <row r="532" spans="1:4">
       <c r="A532">
-        <v>45.2</v>
+        <v>14</v>
       </c>
       <c r="B532">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C532" t="s">
         <v>4</v>
@@ -7830,10 +7830,10 @@
     </row>
     <row r="533" spans="1:4">
       <c r="A533">
-        <v>35.7</v>
+        <v>14</v>
       </c>
       <c r="B533">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C533" t="s">
         <v>4</v>
@@ -7844,10 +7844,10 @@
     </row>
     <row r="534" spans="1:4">
       <c r="A534">
-        <v>18.4</v>
+        <v>12.7</v>
       </c>
       <c r="B534">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C534" t="s">
         <v>4</v>
@@ -7858,10 +7858,10 @@
     </row>
     <row r="535" spans="1:4">
       <c r="A535">
-        <v>48.4</v>
+        <v>20.1</v>
       </c>
       <c r="B535">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C535" t="s">
         <v>4</v>
@@ -7872,10 +7872,10 @@
     </row>
     <row r="536" spans="1:4">
       <c r="A536">
-        <v>44.8</v>
+        <v>13.9</v>
       </c>
       <c r="B536">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C536" t="s">
         <v>4</v>
@@ -7886,10 +7886,10 @@
     </row>
     <row r="537" spans="1:4">
       <c r="A537">
-        <v>12.9</v>
+        <v>19.6</v>
       </c>
       <c r="B537">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="C537" t="s">
         <v>4</v>
@@ -7900,10 +7900,10 @@
     </row>
     <row r="538" spans="1:4">
       <c r="A538">
-        <v>38.7</v>
+        <v>15.2</v>
       </c>
       <c r="B538">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C538" t="s">
         <v>4</v>
@@ -7914,10 +7914,10 @@
     </row>
     <row r="539" spans="1:4">
       <c r="A539">
-        <v>18.2</v>
+        <v>12.6</v>
       </c>
       <c r="B539">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C539" t="s">
         <v>4</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="540" spans="1:4">
       <c r="A540">
-        <v>40.1</v>
+        <v>17.3</v>
       </c>
       <c r="B540">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C540" t="s">
         <v>4</v>
@@ -7942,10 +7942,10 @@
     </row>
     <row r="541" spans="1:4">
       <c r="A541">
-        <v>37.3</v>
+        <v>19.7</v>
       </c>
       <c r="B541">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C541" t="s">
         <v>4</v>
@@ -7956,10 +7956,10 @@
     </row>
     <row r="542" spans="1:4">
       <c r="A542">
-        <v>20.3</v>
+        <v>19.6</v>
       </c>
       <c r="B542">
-        <v>0.079</v>
+        <v>0.2</v>
       </c>
       <c r="C542" t="s">
         <v>4</v>
@@ -7970,10 +7970,10 @@
     </row>
     <row r="543" spans="1:4">
       <c r="A543">
-        <v>39.5</v>
+        <v>15.5</v>
       </c>
       <c r="B543">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C543" t="s">
         <v>4</v>
@@ -7984,10 +7984,10 @@
     </row>
     <row r="544" spans="1:4">
       <c r="A544">
-        <v>69.5</v>
+        <v>13.1</v>
       </c>
       <c r="B544">
-        <v>2.037</v>
+        <v>0.056</v>
       </c>
       <c r="C544" t="s">
         <v>4</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="545" spans="1:4">
       <c r="A545">
-        <v>43.8</v>
+        <v>18.2</v>
       </c>
       <c r="B545">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C545" t="s">
         <v>4</v>
@@ -8012,10 +8012,10 @@
     </row>
     <row r="546" spans="1:4">
       <c r="A546">
-        <v>46.6</v>
+        <v>14.5</v>
       </c>
       <c r="B546">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C546" t="s">
         <v>4</v>
@@ -8026,10 +8026,10 @@
     </row>
     <row r="547" spans="1:4">
       <c r="A547">
-        <v>38.4</v>
+        <v>26.1</v>
       </c>
       <c r="B547">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C547" t="s">
         <v>4</v>
@@ -8040,10 +8040,10 @@
     </row>
     <row r="548" spans="1:4">
       <c r="A548">
-        <v>35.4</v>
+        <v>13.9</v>
       </c>
       <c r="B548">
-        <v>0.713</v>
+        <v>0.095</v>
       </c>
       <c r="C548" t="s">
         <v>4</v>
@@ -8054,10 +8054,10 @@
     </row>
     <row r="549" spans="1:4">
       <c r="A549">
-        <v>57.7</v>
+        <v>7.2</v>
       </c>
       <c r="B549">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="C549" t="s">
         <v>4</v>
@@ -8068,10 +8068,10 @@
     </row>
     <row r="550" spans="1:4">
       <c r="A550">
-        <v>32.4</v>
+        <v>10</v>
       </c>
       <c r="B550">
-        <v>0.469</v>
+        <v>0.051</v>
       </c>
       <c r="C550" t="s">
         <v>4</v>
@@ -8082,10 +8082,10 @@
     </row>
     <row r="551" spans="1:4">
       <c r="A551">
-        <v>26.3</v>
+        <v>13.7</v>
       </c>
       <c r="B551">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C551" t="s">
         <v>4</v>
@@ -8096,10 +8096,10 @@
     </row>
     <row r="552" spans="1:4">
       <c r="A552">
-        <v>27.5</v>
+        <v>14.3</v>
       </c>
       <c r="B552">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C552" t="s">
         <v>4</v>
@@ -8110,10 +8110,10 @@
     </row>
     <row r="553" spans="1:4">
       <c r="A553">
-        <v>14.6</v>
+        <v>22.3</v>
       </c>
       <c r="B553">
-        <v>0.08599999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="C553" t="s">
         <v>4</v>
@@ -8124,10 +8124,10 @@
     </row>
     <row r="554" spans="1:4">
       <c r="A554">
-        <v>31.4</v>
+        <v>16.6</v>
       </c>
       <c r="B554">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C554" t="s">
         <v>4</v>
@@ -8138,10 +8138,10 @@
     </row>
     <row r="555" spans="1:4">
       <c r="A555">
-        <v>22.3</v>
+        <v>21.5</v>
       </c>
       <c r="B555">
-        <v>0.079</v>
+        <v>0.2</v>
       </c>
       <c r="C555" t="s">
         <v>4</v>
@@ -8152,10 +8152,10 @@
     </row>
     <row r="556" spans="1:4">
       <c r="A556">
-        <v>10.6</v>
+        <v>23.4</v>
       </c>
       <c r="B556">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C556" t="s">
         <v>4</v>
@@ -8166,10 +8166,10 @@
     </row>
     <row r="557" spans="1:4">
       <c r="A557">
-        <v>29.6</v>
+        <v>15.4</v>
       </c>
       <c r="B557">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C557" t="s">
         <v>4</v>
@@ -8180,10 +8180,10 @@
     </row>
     <row r="558" spans="1:4">
       <c r="A558">
-        <v>48.3</v>
+        <v>20.1</v>
       </c>
       <c r="B558">
-        <v>0.519</v>
+        <v>0.097</v>
       </c>
       <c r="C558" t="s">
         <v>4</v>
@@ -8194,10 +8194,10 @@
     </row>
     <row r="559" spans="1:4">
       <c r="A559">
-        <v>49.9</v>
+        <v>20.5</v>
       </c>
       <c r="B559">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C559" t="s">
         <v>4</v>
@@ -8208,10 +8208,10 @@
     </row>
     <row r="560" spans="1:4">
       <c r="A560">
-        <v>46.5</v>
+        <v>14.4</v>
       </c>
       <c r="B560">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C560" t="s">
         <v>4</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="561" spans="1:4">
       <c r="A561">
-        <v>40.5</v>
+        <v>27.5</v>
       </c>
       <c r="B561">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C561" t="s">
         <v>4</v>
@@ -8236,10 +8236,10 @@
     </row>
     <row r="562" spans="1:4">
       <c r="A562">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="B562">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C562" t="s">
         <v>4</v>
@@ -8250,10 +8250,10 @@
     </row>
     <row r="563" spans="1:4">
       <c r="A563">
-        <v>54.1</v>
+        <v>22.2</v>
       </c>
       <c r="B563">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C563" t="s">
         <v>4</v>
@@ -8264,10 +8264,10 @@
     </row>
     <row r="564" spans="1:4">
       <c r="A564">
-        <v>49.1</v>
+        <v>15.2</v>
       </c>
       <c r="B564">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C564" t="s">
         <v>4</v>
@@ -8278,10 +8278,10 @@
     </row>
     <row r="565" spans="1:4">
       <c r="A565">
-        <v>41.6</v>
+        <v>17.9</v>
       </c>
       <c r="B565">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C565" t="s">
         <v>4</v>
@@ -8292,10 +8292,10 @@
     </row>
     <row r="566" spans="1:4">
       <c r="A566">
-        <v>20.8</v>
+        <v>10.9</v>
       </c>
       <c r="B566">
-        <v>0.061</v>
+        <v>0.042</v>
       </c>
       <c r="C566" t="s">
         <v>4</v>
@@ -8306,10 +8306,10 @@
     </row>
     <row r="567" spans="1:4">
       <c r="A567">
-        <v>28.9</v>
+        <v>15.1</v>
       </c>
       <c r="B567">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C567" t="s">
         <v>4</v>
@@ -8320,10 +8320,10 @@
     </row>
     <row r="568" spans="1:4">
       <c r="A568">
-        <v>17.8</v>
+        <v>26.5</v>
       </c>
       <c r="B568">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C568" t="s">
         <v>4</v>
@@ -8334,10 +8334,10 @@
     </row>
     <row r="569" spans="1:4">
       <c r="A569">
-        <v>42.6</v>
+        <v>18.3</v>
       </c>
       <c r="B569">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C569" t="s">
         <v>4</v>
@@ -8348,10 +8348,10 @@
     </row>
     <row r="570" spans="1:4">
       <c r="A570">
-        <v>17.7</v>
+        <v>12.3</v>
       </c>
       <c r="B570">
-        <v>0.036</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="C570" t="s">
         <v>4</v>
@@ -8362,10 +8362,10 @@
     </row>
     <row r="571" spans="1:4">
       <c r="A571">
-        <v>17.8</v>
+        <v>26.5</v>
       </c>
       <c r="B571">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C571" t="s">
         <v>4</v>
@@ -8376,10 +8376,10 @@
     </row>
     <row r="572" spans="1:4">
       <c r="A572">
-        <v>37.1</v>
+        <v>11.4</v>
       </c>
       <c r="B572">
-        <v>0.469</v>
+        <v>0.051</v>
       </c>
       <c r="C572" t="s">
         <v>4</v>
@@ -8390,10 +8390,10 @@
     </row>
     <row r="573" spans="1:4">
       <c r="A573">
-        <v>21.1</v>
+        <v>19.6</v>
       </c>
       <c r="B573">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C573" t="s">
         <v>4</v>
@@ -8404,10 +8404,10 @@
     </row>
     <row r="574" spans="1:4">
       <c r="A574">
-        <v>37.4</v>
+        <v>25.4</v>
       </c>
       <c r="B574">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C574" t="s">
         <v>4</v>
@@ -8418,10 +8418,10 @@
     </row>
     <row r="575" spans="1:4">
       <c r="A575">
-        <v>62.5</v>
+        <v>11.8</v>
       </c>
       <c r="B575">
-        <v>2.037</v>
+        <v>0.056</v>
       </c>
       <c r="C575" t="s">
         <v>4</v>
@@ -8432,10 +8432,10 @@
     </row>
     <row r="576" spans="1:4">
       <c r="A576">
-        <v>29</v>
+        <v>15.1</v>
       </c>
       <c r="B576">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C576" t="s">
         <v>4</v>
@@ -8446,10 +8446,10 @@
     </row>
     <row r="577" spans="1:4">
       <c r="A577">
-        <v>31.7</v>
+        <v>16.7</v>
       </c>
       <c r="B577">
-        <v>0.45</v>
+        <v>0.08</v>
       </c>
       <c r="C577" t="s">
         <v>4</v>
@@ -8460,10 +8460,10 @@
     </row>
     <row r="578" spans="1:4">
       <c r="A578">
-        <v>54.5</v>
+        <v>22.3</v>
       </c>
       <c r="B578">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C578" t="s">
         <v>4</v>
@@ -8474,10 +8474,10 @@
     </row>
     <row r="579" spans="1:4">
       <c r="A579">
-        <v>20.4</v>
+        <v>22.1</v>
       </c>
       <c r="B579">
-        <v>0.077</v>
+        <v>0.138</v>
       </c>
       <c r="C579" t="s">
         <v>4</v>
@@ -8488,10 +8488,10 @@
     </row>
     <row r="580" spans="1:4">
       <c r="A580">
-        <v>37.1</v>
+        <v>25.2</v>
       </c>
       <c r="B580">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C580" t="s">
         <v>4</v>
@@ -8502,10 +8502,10 @@
     </row>
     <row r="581" spans="1:4">
       <c r="A581">
-        <v>10</v>
+        <v>22.2</v>
       </c>
       <c r="B581">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C581" t="s">
         <v>4</v>
@@ -8516,10 +8516,10 @@
     </row>
     <row r="582" spans="1:4">
       <c r="A582">
-        <v>49.7</v>
+        <v>20.4</v>
       </c>
       <c r="B582">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C582" t="s">
         <v>4</v>
@@ -8530,10 +8530,10 @@
     </row>
     <row r="583" spans="1:4">
       <c r="A583">
-        <v>28.1</v>
+        <v>14.6</v>
       </c>
       <c r="B583">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C583" t="s">
         <v>4</v>
@@ -8544,10 +8544,10 @@
     </row>
     <row r="584" spans="1:4">
       <c r="A584">
-        <v>16.9</v>
+        <v>25.1</v>
       </c>
       <c r="B584">
-        <v>0.031</v>
+        <v>0.481</v>
       </c>
       <c r="C584" t="s">
         <v>4</v>
@@ -8558,10 +8558,10 @@
     </row>
     <row r="585" spans="1:4">
       <c r="A585">
-        <v>36.1</v>
+        <v>24.6</v>
       </c>
       <c r="B585">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C585" t="s">
         <v>4</v>
@@ -8572,10 +8572,10 @@
     </row>
     <row r="586" spans="1:4">
       <c r="A586">
-        <v>23.8</v>
+        <v>22.1</v>
       </c>
       <c r="B586">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C586" t="s">
         <v>4</v>
@@ -8586,10 +8586,10 @@
     </row>
     <row r="587" spans="1:4">
       <c r="A587">
-        <v>22</v>
+        <v>21.2</v>
       </c>
       <c r="B587">
-        <v>0.079</v>
+        <v>0.2</v>
       </c>
       <c r="C587" t="s">
         <v>4</v>
@@ -8600,10 +8600,10 @@
     </row>
     <row r="588" spans="1:4">
       <c r="A588">
-        <v>62.4</v>
+        <v>11.8</v>
       </c>
       <c r="B588">
-        <v>2.037</v>
+        <v>0.056</v>
       </c>
       <c r="C588" t="s">
         <v>4</v>
@@ -8614,10 +8614,10 @@
     </row>
     <row r="589" spans="1:4">
       <c r="A589">
-        <v>10.5</v>
+        <v>23.2</v>
       </c>
       <c r="B589">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C589" t="s">
         <v>4</v>
@@ -8628,10 +8628,10 @@
     </row>
     <row r="590" spans="1:4">
       <c r="A590">
-        <v>10.4</v>
+        <v>23.1</v>
       </c>
       <c r="B590">
-        <v>0.036</v>
+        <v>0.12</v>
       </c>
       <c r="C590" t="s">
         <v>4</v>
@@ -8642,10 +8642,10 @@
     </row>
     <row r="591" spans="1:4">
       <c r="A591">
-        <v>40.6</v>
+        <v>27.6</v>
       </c>
       <c r="B591">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C591" t="s">
         <v>4</v>
@@ -8656,10 +8656,10 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592">
-        <v>46.9</v>
+        <v>14.6</v>
       </c>
       <c r="B592">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C592" t="s">
         <v>4</v>
@@ -8670,10 +8670,10 @@
     </row>
     <row r="593" spans="1:4">
       <c r="A593">
-        <v>47.6</v>
+        <v>14.8</v>
       </c>
       <c r="B593">
-        <v>0.513</v>
+        <v>0.138</v>
       </c>
       <c r="C593" t="s">
         <v>4</v>
@@ -8684,10 +8684,10 @@
     </row>
     <row r="594" spans="1:4">
       <c r="A594">
-        <v>61.3</v>
+        <v>7.7</v>
       </c>
       <c r="B594">
-        <v>1.49</v>
+        <v>0.06</v>
       </c>
       <c r="C594" t="s">
         <v>4</v>
@@ -8698,10 +8698,10 @@
     </row>
     <row r="595" spans="1:4">
       <c r="A595">
-        <v>8.6</v>
+        <v>25.5</v>
       </c>
       <c r="B595">
-        <v>0.036</v>
+        <v>0.197</v>
       </c>
       <c r="C595" t="s">
         <v>4</v>
@@ -8712,10 +8712,10 @@
     </row>
     <row r="596" spans="1:4">
       <c r="A596">
-        <v>30.9</v>
+        <v>16.1</v>
       </c>
       <c r="B596">
-        <v>0.23</v>
+        <v>0.124</v>
       </c>
       <c r="C596" t="s">
         <v>4</v>
@@ -8726,10 +8726,10 @@
     </row>
     <row r="597" spans="1:4">
       <c r="A597">
-        <v>8.6</v>
+        <v>25.6</v>
       </c>
       <c r="B597">
-        <v>0.036</v>
+        <v>0.197</v>
       </c>
       <c r="C597" t="s">
         <v>4</v>
@@ -8740,10 +8740,10 @@
     </row>
     <row r="598" spans="1:4">
       <c r="A598">
-        <v>51.9</v>
+        <v>21.3</v>
       </c>
       <c r="B598">
-        <v>1.19</v>
+        <v>0.204</v>
       </c>
       <c r="C598" t="s">
         <v>4</v>
@@ -8754,10 +8754,10 @@
     </row>
     <row r="599" spans="1:4">
       <c r="A599">
-        <v>42.4</v>
+        <v>18.2</v>
       </c>
       <c r="B599">
-        <v>1.115</v>
+        <v>0.114</v>
       </c>
       <c r="C599" t="s">
         <v>4</v>
@@ -8768,10 +8768,10 @@
     </row>
     <row r="600" spans="1:4">
       <c r="A600">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="B600">
-        <v>0.082</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C600" t="s">
         <v>4</v>
@@ -8782,10 +8782,10 @@
     </row>
     <row r="601" spans="1:4">
       <c r="A601">
-        <v>39.4</v>
+        <v>26.8</v>
       </c>
       <c r="B601">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C601" t="s">
         <v>4</v>
@@ -8796,10 +8796,10 @@
     </row>
     <row r="602" spans="1:4">
       <c r="A602">
-        <v>13.3</v>
+        <v>31.4</v>
       </c>
       <c r="B602">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C602" t="s">
         <v>5</v>
@@ -8810,10 +8810,10 @@
     </row>
     <row r="603" spans="1:4">
       <c r="A603">
-        <v>10.6</v>
+        <v>7.9</v>
       </c>
       <c r="B603">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C603" t="s">
         <v>5</v>
@@ -8824,10 +8824,10 @@
     </row>
     <row r="604" spans="1:4">
       <c r="A604">
-        <v>21.8</v>
+        <v>6.5</v>
       </c>
       <c r="B604">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C604" t="s">
         <v>5</v>
@@ -8838,10 +8838,10 @@
     </row>
     <row r="605" spans="1:4">
       <c r="A605">
-        <v>23.2</v>
+        <v>7</v>
       </c>
       <c r="B605">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C605" t="s">
         <v>5</v>
@@ -8852,10 +8852,10 @@
     </row>
     <row r="606" spans="1:4">
       <c r="A606">
-        <v>9</v>
+        <v>26.7</v>
       </c>
       <c r="B606">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C606" t="s">
         <v>5</v>
@@ -8866,10 +8866,10 @@
     </row>
     <row r="607" spans="1:4">
       <c r="A607">
-        <v>21.7</v>
+        <v>16.4</v>
       </c>
       <c r="B607">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C607" t="s">
         <v>5</v>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="608" spans="1:4">
       <c r="A608">
-        <v>14.4</v>
+        <v>35.2</v>
       </c>
       <c r="B608">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C608" t="s">
         <v>5</v>
@@ -8894,10 +8894,10 @@
     </row>
     <row r="609" spans="1:4">
       <c r="A609">
-        <v>12.1</v>
+        <v>29.5</v>
       </c>
       <c r="B609">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C609" t="s">
         <v>5</v>
@@ -8908,10 +8908,10 @@
     </row>
     <row r="610" spans="1:4">
       <c r="A610">
-        <v>22.7</v>
+        <v>24.8</v>
       </c>
       <c r="B610">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C610" t="s">
         <v>5</v>
@@ -8922,10 +8922,10 @@
     </row>
     <row r="611" spans="1:4">
       <c r="A611">
-        <v>15.7</v>
+        <v>23.8</v>
       </c>
       <c r="B611">
-        <v>0.229</v>
+        <v>0.374</v>
       </c>
       <c r="C611" t="s">
         <v>5</v>
@@ -8936,10 +8936,10 @@
     </row>
     <row r="612" spans="1:4">
       <c r="A612">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="B612">
-        <v>0.209</v>
+        <v>0.208</v>
       </c>
       <c r="C612" t="s">
         <v>5</v>
@@ -8950,10 +8950,10 @@
     </row>
     <row r="613" spans="1:4">
       <c r="A613">
-        <v>9.4</v>
+        <v>27.9</v>
       </c>
       <c r="B613">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C613" t="s">
         <v>5</v>
@@ -8964,10 +8964,10 @@
     </row>
     <row r="614" spans="1:4">
       <c r="A614">
-        <v>22.8</v>
+        <v>6.8</v>
       </c>
       <c r="B614">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C614" t="s">
         <v>5</v>
@@ -8978,10 +8978,10 @@
     </row>
     <row r="615" spans="1:4">
       <c r="A615">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="B615">
-        <v>1.153</v>
+        <v>0.668</v>
       </c>
       <c r="C615" t="s">
         <v>5</v>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="616" spans="1:4">
       <c r="A616">
-        <v>17.5</v>
+        <v>20.3</v>
       </c>
       <c r="B616">
-        <v>0.271</v>
+        <v>0.262</v>
       </c>
       <c r="C616" t="s">
         <v>5</v>
@@ -9006,10 +9006,10 @@
     </row>
     <row r="617" spans="1:4">
       <c r="A617">
-        <v>24.5</v>
+        <v>11.3</v>
       </c>
       <c r="B617">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C617" t="s">
         <v>5</v>
@@ -9020,10 +9020,10 @@
     </row>
     <row r="618" spans="1:4">
       <c r="A618">
-        <v>25.5</v>
+        <v>11.7</v>
       </c>
       <c r="B618">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C618" t="s">
         <v>5</v>
@@ -9034,10 +9034,10 @@
     </row>
     <row r="619" spans="1:4">
       <c r="A619">
-        <v>17.3</v>
+        <v>11.4</v>
       </c>
       <c r="B619">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="C619" t="s">
         <v>5</v>
@@ -9048,10 +9048,10 @@
     </row>
     <row r="620" spans="1:4">
       <c r="A620">
-        <v>25.2</v>
+        <v>11.6</v>
       </c>
       <c r="B620">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C620" t="s">
         <v>5</v>
@@ -9062,10 +9062,10 @@
     </row>
     <row r="621" spans="1:4">
       <c r="A621">
-        <v>21.2</v>
+        <v>25</v>
       </c>
       <c r="B621">
-        <v>0.586</v>
+        <v>0.203</v>
       </c>
       <c r="C621" t="s">
         <v>5</v>
@@ -9076,10 +9076,10 @@
     </row>
     <row r="622" spans="1:4">
       <c r="A622">
-        <v>9.6</v>
+        <v>7.1</v>
       </c>
       <c r="B622">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C622" t="s">
         <v>5</v>
@@ -9090,10 +9090,10 @@
     </row>
     <row r="623" spans="1:4">
       <c r="A623">
-        <v>23.1</v>
+        <v>27</v>
       </c>
       <c r="B623">
-        <v>0.863</v>
+        <v>1.362</v>
       </c>
       <c r="C623" t="s">
         <v>5</v>
@@ -9104,10 +9104,10 @@
     </row>
     <row r="624" spans="1:4">
       <c r="A624">
-        <v>15.6</v>
+        <v>23.6</v>
       </c>
       <c r="B624">
-        <v>0.229</v>
+        <v>0.374</v>
       </c>
       <c r="C624" t="s">
         <v>5</v>
@@ -9118,10 +9118,10 @@
     </row>
     <row r="625" spans="1:4">
       <c r="A625">
-        <v>11.7</v>
+        <v>27.4</v>
       </c>
       <c r="B625">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C625" t="s">
         <v>5</v>
@@ -9132,10 +9132,10 @@
     </row>
     <row r="626" spans="1:4">
       <c r="A626">
-        <v>19.4</v>
+        <v>23</v>
       </c>
       <c r="B626">
-        <v>0.586</v>
+        <v>0.203</v>
       </c>
       <c r="C626" t="s">
         <v>5</v>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="627" spans="1:4">
       <c r="A627">
-        <v>19.7</v>
+        <v>22.8</v>
       </c>
       <c r="B627">
-        <v>0.271</v>
+        <v>0.262</v>
       </c>
       <c r="C627" t="s">
         <v>5</v>
@@ -9160,10 +9160,10 @@
     </row>
     <row r="628" spans="1:4">
       <c r="A628">
-        <v>9.4</v>
+        <v>27.8</v>
       </c>
       <c r="B628">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C628" t="s">
         <v>5</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="629" spans="1:4">
       <c r="A629">
-        <v>21.3</v>
+        <v>25.1</v>
       </c>
       <c r="B629">
-        <v>0.586</v>
+        <v>0.203</v>
       </c>
       <c r="C629" t="s">
         <v>5</v>
@@ -9188,10 +9188,10 @@
     </row>
     <row r="630" spans="1:4">
       <c r="A630">
-        <v>16.7</v>
+        <v>11</v>
       </c>
       <c r="B630">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="C630" t="s">
         <v>5</v>
@@ -9202,10 +9202,10 @@
     </row>
     <row r="631" spans="1:4">
       <c r="A631">
-        <v>10.5</v>
+        <v>7.7</v>
       </c>
       <c r="B631">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C631" t="s">
         <v>5</v>
@@ -9216,10 +9216,10 @@
     </row>
     <row r="632" spans="1:4">
       <c r="A632">
-        <v>14.2</v>
+        <v>21.5</v>
       </c>
       <c r="B632">
-        <v>0.229</v>
+        <v>0.374</v>
       </c>
       <c r="C632" t="s">
         <v>5</v>
@@ -9230,10 +9230,10 @@
     </row>
     <row r="633" spans="1:4">
       <c r="A633">
-        <v>1</v>
+        <v>18.2</v>
       </c>
       <c r="B633">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C633" t="s">
         <v>5</v>
@@ -9244,10 +9244,10 @@
     </row>
     <row r="634" spans="1:4">
       <c r="A634">
-        <v>10.8</v>
+        <v>25.5</v>
       </c>
       <c r="B634">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C634" t="s">
         <v>5</v>
@@ -9258,10 +9258,10 @@
     </row>
     <row r="635" spans="1:4">
       <c r="A635">
-        <v>11.5</v>
+        <v>13.8</v>
       </c>
       <c r="B635">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C635" t="s">
         <v>5</v>
@@ -9272,10 +9272,10 @@
     </row>
     <row r="636" spans="1:4">
       <c r="A636">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="B636">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C636" t="s">
         <v>5</v>
@@ -9286,10 +9286,10 @@
     </row>
     <row r="637" spans="1:4">
       <c r="A637">
-        <v>15.6</v>
+        <v>23.7</v>
       </c>
       <c r="B637">
-        <v>0.229</v>
+        <v>0.374</v>
       </c>
       <c r="C637" t="s">
         <v>5</v>
@@ -9300,10 +9300,10 @@
     </row>
     <row r="638" spans="1:4">
       <c r="A638">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="B638">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C638" t="s">
         <v>5</v>
@@ -9314,10 +9314,10 @@
     </row>
     <row r="639" spans="1:4">
       <c r="A639">
-        <v>20.3</v>
+        <v>22.1</v>
       </c>
       <c r="B639">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C639" t="s">
         <v>5</v>
@@ -9328,10 +9328,10 @@
     </row>
     <row r="640" spans="1:4">
       <c r="A640">
-        <v>12</v>
+        <v>14.4</v>
       </c>
       <c r="B640">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C640" t="s">
         <v>5</v>
@@ -9342,10 +9342,10 @@
     </row>
     <row r="641" spans="1:4">
       <c r="A641">
-        <v>9.199999999999999</v>
+        <v>27.2</v>
       </c>
       <c r="B641">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C641" t="s">
         <v>5</v>
@@ -9356,10 +9356,10 @@
     </row>
     <row r="642" spans="1:4">
       <c r="A642">
-        <v>10.2</v>
+        <v>7.5</v>
       </c>
       <c r="B642">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C642" t="s">
         <v>5</v>
@@ -9370,10 +9370,10 @@
     </row>
     <row r="643" spans="1:4">
       <c r="A643">
-        <v>22.2</v>
+        <v>16.8</v>
       </c>
       <c r="B643">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C643" t="s">
         <v>5</v>
@@ -9384,10 +9384,10 @@
     </row>
     <row r="644" spans="1:4">
       <c r="A644">
-        <v>10.6</v>
+        <v>7.9</v>
       </c>
       <c r="B644">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C644" t="s">
         <v>5</v>
@@ -9398,10 +9398,10 @@
     </row>
     <row r="645" spans="1:4">
       <c r="A645">
-        <v>22.8</v>
+        <v>6.9</v>
       </c>
       <c r="B645">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C645" t="s">
         <v>5</v>
@@ -9412,10 +9412,10 @@
     </row>
     <row r="646" spans="1:4">
       <c r="A646">
-        <v>19.4</v>
+        <v>30.3</v>
       </c>
       <c r="B646">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C646" t="s">
         <v>5</v>
@@ -9426,10 +9426,10 @@
     </row>
     <row r="647" spans="1:4">
       <c r="A647">
-        <v>10.9</v>
+        <v>8</v>
       </c>
       <c r="B647">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C647" t="s">
         <v>5</v>
@@ -9440,10 +9440,10 @@
     </row>
     <row r="648" spans="1:4">
       <c r="A648">
-        <v>23.7</v>
+        <v>7.1</v>
       </c>
       <c r="B648">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C648" t="s">
         <v>5</v>
@@ -9454,10 +9454,10 @@
     </row>
     <row r="649" spans="1:4">
       <c r="A649">
-        <v>12</v>
+        <v>14.4</v>
       </c>
       <c r="B649">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C649" t="s">
         <v>5</v>
@@ -9468,10 +9468,10 @@
     </row>
     <row r="650" spans="1:4">
       <c r="A650">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B650">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C650" t="s">
         <v>5</v>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="651" spans="1:4">
       <c r="A651">
-        <v>21.3</v>
+        <v>23.3</v>
       </c>
       <c r="B651">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C651" t="s">
         <v>5</v>
@@ -9496,10 +9496,10 @@
     </row>
     <row r="652" spans="1:4">
       <c r="A652">
-        <v>25.4</v>
+        <v>11.7</v>
       </c>
       <c r="B652">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C652" t="s">
         <v>5</v>
@@ -9510,10 +9510,10 @@
     </row>
     <row r="653" spans="1:4">
       <c r="A653">
-        <v>10.4</v>
+        <v>7.7</v>
       </c>
       <c r="B653">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C653" t="s">
         <v>5</v>
@@ -9524,10 +9524,10 @@
     </row>
     <row r="654" spans="1:4">
       <c r="A654">
-        <v>20.8</v>
+        <v>15.7</v>
       </c>
       <c r="B654">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C654" t="s">
         <v>5</v>
@@ -9538,10 +9538,10 @@
     </row>
     <row r="655" spans="1:4">
       <c r="A655">
-        <v>20.5</v>
+        <v>24.2</v>
       </c>
       <c r="B655">
-        <v>0.586</v>
+        <v>0.203</v>
       </c>
       <c r="C655" t="s">
         <v>5</v>
@@ -9552,10 +9552,10 @@
     </row>
     <row r="656" spans="1:4">
       <c r="A656">
-        <v>12.1</v>
+        <v>14.5</v>
       </c>
       <c r="B656">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C656" t="s">
         <v>5</v>
@@ -9566,10 +9566,10 @@
     </row>
     <row r="657" spans="1:4">
       <c r="A657">
-        <v>1</v>
+        <v>18.7</v>
       </c>
       <c r="B657">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C657" t="s">
         <v>5</v>
@@ -9580,10 +9580,10 @@
     </row>
     <row r="658" spans="1:4">
       <c r="A658">
-        <v>9.300000000000001</v>
+        <v>27.6</v>
       </c>
       <c r="B658">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C658" t="s">
         <v>5</v>
@@ -9594,10 +9594,10 @@
     </row>
     <row r="659" spans="1:4">
       <c r="A659">
-        <v>21.7</v>
+        <v>25.4</v>
       </c>
       <c r="B659">
-        <v>0.863</v>
+        <v>1.362</v>
       </c>
       <c r="C659" t="s">
         <v>5</v>
@@ -9608,10 +9608,10 @@
     </row>
     <row r="660" spans="1:4">
       <c r="A660">
-        <v>23</v>
+        <v>26.9</v>
       </c>
       <c r="B660">
-        <v>0.863</v>
+        <v>1.362</v>
       </c>
       <c r="C660" t="s">
         <v>5</v>
@@ -9622,10 +9622,10 @@
     </row>
     <row r="661" spans="1:4">
       <c r="A661">
-        <v>9.6</v>
+        <v>28.5</v>
       </c>
       <c r="B661">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C661" t="s">
         <v>5</v>
@@ -9636,10 +9636,10 @@
     </row>
     <row r="662" spans="1:4">
       <c r="A662">
-        <v>23.4</v>
+        <v>7</v>
       </c>
       <c r="B662">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C662" t="s">
         <v>5</v>
@@ -9650,10 +9650,10 @@
     </row>
     <row r="663" spans="1:4">
       <c r="A663">
-        <v>11.3</v>
+        <v>13.5</v>
       </c>
       <c r="B663">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C663" t="s">
         <v>5</v>
@@ -9664,10 +9664,10 @@
     </row>
     <row r="664" spans="1:4">
       <c r="A664">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="B664">
-        <v>1.153</v>
+        <v>0.668</v>
       </c>
       <c r="C664" t="s">
         <v>5</v>
@@ -9678,10 +9678,10 @@
     </row>
     <row r="665" spans="1:4">
       <c r="A665">
-        <v>37.3</v>
+        <v>31.8</v>
       </c>
       <c r="B665">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C665" t="s">
         <v>5</v>
@@ -9692,10 +9692,10 @@
     </row>
     <row r="666" spans="1:4">
       <c r="A666">
-        <v>15.1</v>
+        <v>22.9</v>
       </c>
       <c r="B666">
-        <v>0.229</v>
+        <v>0.374</v>
       </c>
       <c r="C666" t="s">
         <v>5</v>
@@ -9706,10 +9706,10 @@
     </row>
     <row r="667" spans="1:4">
       <c r="A667">
-        <v>22.4</v>
+        <v>16.9</v>
       </c>
       <c r="B667">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C667" t="s">
         <v>5</v>
@@ -9720,10 +9720,10 @@
     </row>
     <row r="668" spans="1:4">
       <c r="A668">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="B668">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C668" t="s">
         <v>5</v>
@@ -9734,10 +9734,10 @@
     </row>
     <row r="669" spans="1:4">
       <c r="A669">
-        <v>1.1</v>
+        <v>19</v>
       </c>
       <c r="B669">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C669" t="s">
         <v>5</v>
@@ -9748,10 +9748,10 @@
     </row>
     <row r="670" spans="1:4">
       <c r="A670">
-        <v>11.1</v>
+        <v>22.1</v>
       </c>
       <c r="B670">
-        <v>0.161</v>
+        <v>0.263</v>
       </c>
       <c r="C670" t="s">
         <v>5</v>
@@ -9762,10 +9762,10 @@
     </row>
     <row r="671" spans="1:4">
       <c r="A671">
-        <v>1</v>
+        <v>18.7</v>
       </c>
       <c r="B671">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C671" t="s">
         <v>5</v>
@@ -9776,10 +9776,10 @@
     </row>
     <row r="672" spans="1:4">
       <c r="A672">
-        <v>21.5</v>
+        <v>16.3</v>
       </c>
       <c r="B672">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C672" t="s">
         <v>5</v>
@@ -9790,10 +9790,10 @@
     </row>
     <row r="673" spans="1:4">
       <c r="A673">
-        <v>18.3</v>
+        <v>12.1</v>
       </c>
       <c r="B673">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="C673" t="s">
         <v>5</v>
@@ -9804,10 +9804,10 @@
     </row>
     <row r="674" spans="1:4">
       <c r="A674">
-        <v>20.7</v>
+        <v>15.7</v>
       </c>
       <c r="B674">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C674" t="s">
         <v>5</v>
@@ -9818,10 +9818,10 @@
     </row>
     <row r="675" spans="1:4">
       <c r="A675">
-        <v>39.6</v>
+        <v>33.7</v>
       </c>
       <c r="B675">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C675" t="s">
         <v>5</v>
@@ -9832,10 +9832,10 @@
     </row>
     <row r="676" spans="1:4">
       <c r="A676">
-        <v>9.6</v>
+        <v>28.5</v>
       </c>
       <c r="B676">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C676" t="s">
         <v>5</v>
@@ -9846,10 +9846,10 @@
     </row>
     <row r="677" spans="1:4">
       <c r="A677">
-        <v>12.3</v>
+        <v>30.1</v>
       </c>
       <c r="B677">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C677" t="s">
         <v>5</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="678" spans="1:4">
       <c r="A678">
-        <v>15.8</v>
+        <v>10.4</v>
       </c>
       <c r="B678">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="C678" t="s">
         <v>5</v>
@@ -9874,10 +9874,10 @@
     </row>
     <row r="679" spans="1:4">
       <c r="A679">
-        <v>13.8</v>
+        <v>33.9</v>
       </c>
       <c r="B679">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C679" t="s">
         <v>5</v>
@@ -9888,10 +9888,10 @@
     </row>
     <row r="680" spans="1:4">
       <c r="A680">
-        <v>8.6</v>
+        <v>25.3</v>
       </c>
       <c r="B680">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C680" t="s">
         <v>5</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="681" spans="1:4">
       <c r="A681">
-        <v>23.4</v>
+        <v>27.4</v>
       </c>
       <c r="B681">
-        <v>0.863</v>
+        <v>1.362</v>
       </c>
       <c r="C681" t="s">
         <v>5</v>
@@ -9916,10 +9916,10 @@
     </row>
     <row r="682" spans="1:4">
       <c r="A682">
-        <v>17.8</v>
+        <v>11.7</v>
       </c>
       <c r="B682">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="C682" t="s">
         <v>5</v>
@@ -9930,10 +9930,10 @@
     </row>
     <row r="683" spans="1:4">
       <c r="A683">
-        <v>12</v>
+        <v>28.2</v>
       </c>
       <c r="B683">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C683" t="s">
         <v>5</v>
@@ -9944,10 +9944,10 @@
     </row>
     <row r="684" spans="1:4">
       <c r="A684">
-        <v>17.8</v>
+        <v>20.6</v>
       </c>
       <c r="B684">
-        <v>0.271</v>
+        <v>0.262</v>
       </c>
       <c r="C684" t="s">
         <v>5</v>
@@ -9958,10 +9958,10 @@
     </row>
     <row r="685" spans="1:4">
       <c r="A685">
-        <v>14.8</v>
+        <v>36.3</v>
       </c>
       <c r="B685">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C685" t="s">
         <v>5</v>
@@ -9972,10 +9972,10 @@
     </row>
     <row r="686" spans="1:4">
       <c r="A686">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="B686">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C686" t="s">
         <v>5</v>
@@ -9986,10 +9986,10 @@
     </row>
     <row r="687" spans="1:4">
       <c r="A687">
-        <v>20.9</v>
+        <v>15.8</v>
       </c>
       <c r="B687">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C687" t="s">
         <v>5</v>
@@ -10000,10 +10000,10 @@
     </row>
     <row r="688" spans="1:4">
       <c r="A688">
-        <v>22.7</v>
+        <v>24.8</v>
       </c>
       <c r="B688">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C688" t="s">
         <v>5</v>
@@ -10014,10 +10014,10 @@
     </row>
     <row r="689" spans="1:4">
       <c r="A689">
-        <v>21.8</v>
+        <v>6.5</v>
       </c>
       <c r="B689">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C689" t="s">
         <v>5</v>
@@ -10028,10 +10028,10 @@
     </row>
     <row r="690" spans="1:4">
       <c r="A690">
-        <v>9</v>
+        <v>26.7</v>
       </c>
       <c r="B690">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C690" t="s">
         <v>5</v>
@@ -10042,10 +10042,10 @@
     </row>
     <row r="691" spans="1:4">
       <c r="A691">
-        <v>22.7</v>
+        <v>6.8</v>
       </c>
       <c r="B691">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C691" t="s">
         <v>5</v>
@@ -10056,10 +10056,10 @@
     </row>
     <row r="692" spans="1:4">
       <c r="A692">
-        <v>12</v>
+        <v>28.2</v>
       </c>
       <c r="B692">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C692" t="s">
         <v>5</v>
@@ -10070,10 +10070,10 @@
     </row>
     <row r="693" spans="1:4">
       <c r="A693">
-        <v>38.2</v>
+        <v>32.5</v>
       </c>
       <c r="B693">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C693" t="s">
         <v>5</v>
@@ -10084,10 +10084,10 @@
     </row>
     <row r="694" spans="1:4">
       <c r="A694">
-        <v>17.7</v>
+        <v>20.9</v>
       </c>
       <c r="B694">
-        <v>0.586</v>
+        <v>0.203</v>
       </c>
       <c r="C694" t="s">
         <v>5</v>
@@ -10098,10 +10098,10 @@
     </row>
     <row r="695" spans="1:4">
       <c r="A695">
-        <v>1.1</v>
+        <v>20</v>
       </c>
       <c r="B695">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C695" t="s">
         <v>5</v>
@@ -10112,10 +10112,10 @@
     </row>
     <row r="696" spans="1:4">
       <c r="A696">
-        <v>28.8</v>
+        <v>28.5</v>
       </c>
       <c r="B696">
-        <v>1.153</v>
+        <v>0.668</v>
       </c>
       <c r="C696" t="s">
         <v>5</v>
@@ -10126,10 +10126,10 @@
     </row>
     <row r="697" spans="1:4">
       <c r="A697">
-        <v>22.1</v>
+        <v>16.8</v>
       </c>
       <c r="B697">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C697" t="s">
         <v>5</v>
@@ -10140,10 +10140,10 @@
     </row>
     <row r="698" spans="1:4">
       <c r="A698">
-        <v>8.800000000000001</v>
+        <v>26.1</v>
       </c>
       <c r="B698">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C698" t="s">
         <v>5</v>
@@ -10154,10 +10154,10 @@
     </row>
     <row r="699" spans="1:4">
       <c r="A699">
-        <v>10.2</v>
+        <v>7.6</v>
       </c>
       <c r="B699">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C699" t="s">
         <v>5</v>
@@ -10168,10 +10168,10 @@
     </row>
     <row r="700" spans="1:4">
       <c r="A700">
-        <v>41.2</v>
+        <v>35.1</v>
       </c>
       <c r="B700">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C700" t="s">
         <v>5</v>
@@ -10182,10 +10182,10 @@
     </row>
     <row r="701" spans="1:4">
       <c r="A701">
-        <v>26.4</v>
+        <v>12.1</v>
       </c>
       <c r="B701">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C701" t="s">
         <v>5</v>
@@ -10196,10 +10196,10 @@
     </row>
     <row r="702" spans="1:4">
       <c r="A702">
-        <v>26.3</v>
+        <v>12.1</v>
       </c>
       <c r="B702">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C702" t="s">
         <v>5</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="703" spans="1:4">
       <c r="A703">
-        <v>12.5</v>
+        <v>29.5</v>
       </c>
       <c r="B703">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C703" t="s">
         <v>5</v>
@@ -10224,10 +10224,10 @@
     </row>
     <row r="704" spans="1:4">
       <c r="A704">
-        <v>13.4</v>
+        <v>32.7</v>
       </c>
       <c r="B704">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C704" t="s">
         <v>5</v>
@@ -10238,10 +10238,10 @@
     </row>
     <row r="705" spans="1:4">
       <c r="A705">
-        <v>23.7</v>
+        <v>7.1</v>
       </c>
       <c r="B705">
-        <v>0.328</v>
+        <v>0.101</v>
       </c>
       <c r="C705" t="s">
         <v>5</v>
@@ -10252,10 +10252,10 @@
     </row>
     <row r="706" spans="1:4">
       <c r="A706">
-        <v>1.2</v>
+        <v>20.9</v>
       </c>
       <c r="B706">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C706" t="s">
         <v>5</v>
@@ -10266,10 +10266,10 @@
     </row>
     <row r="707" spans="1:4">
       <c r="A707">
-        <v>17.7</v>
+        <v>27.7</v>
       </c>
       <c r="B707">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C707" t="s">
         <v>5</v>
@@ -10280,10 +10280,10 @@
     </row>
     <row r="708" spans="1:4">
       <c r="A708">
-        <v>21.9</v>
+        <v>23.9</v>
       </c>
       <c r="B708">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C708" t="s">
         <v>5</v>
@@ -10294,10 +10294,10 @@
     </row>
     <row r="709" spans="1:4">
       <c r="A709">
-        <v>14.3</v>
+        <v>35</v>
       </c>
       <c r="B709">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C709" t="s">
         <v>5</v>
@@ -10308,10 +10308,10 @@
     </row>
     <row r="710" spans="1:4">
       <c r="A710">
-        <v>12.4</v>
+        <v>14.9</v>
       </c>
       <c r="B710">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C710" t="s">
         <v>5</v>
@@ -10322,10 +10322,10 @@
     </row>
     <row r="711" spans="1:4">
       <c r="A711">
-        <v>36.7</v>
+        <v>31.2</v>
       </c>
       <c r="B711">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C711" t="s">
         <v>5</v>
@@ -10336,10 +10336,10 @@
     </row>
     <row r="712" spans="1:4">
       <c r="A712">
-        <v>12.8</v>
+        <v>25.4</v>
       </c>
       <c r="B712">
-        <v>0.161</v>
+        <v>0.263</v>
       </c>
       <c r="C712" t="s">
         <v>5</v>
@@ -10350,10 +10350,10 @@
     </row>
     <row r="713" spans="1:4">
       <c r="A713">
-        <v>11.8</v>
+        <v>27.8</v>
       </c>
       <c r="B713">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C713" t="s">
         <v>5</v>
@@ -10364,10 +10364,10 @@
     </row>
     <row r="714" spans="1:4">
       <c r="A714">
-        <v>20.3</v>
+        <v>23.9</v>
       </c>
       <c r="B714">
-        <v>0.586</v>
+        <v>0.203</v>
       </c>
       <c r="C714" t="s">
         <v>5</v>
@@ -10378,10 +10378,10 @@
     </row>
     <row r="715" spans="1:4">
       <c r="A715">
-        <v>9.699999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="B715">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C715" t="s">
         <v>5</v>
@@ -10392,10 +10392,10 @@
     </row>
     <row r="716" spans="1:4">
       <c r="A716">
-        <v>1</v>
+        <v>17.8</v>
       </c>
       <c r="B716">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C716" t="s">
         <v>5</v>
@@ -10406,10 +10406,10 @@
     </row>
     <row r="717" spans="1:4">
       <c r="A717">
-        <v>1.1</v>
+        <v>20.2</v>
       </c>
       <c r="B717">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C717" t="s">
         <v>5</v>
@@ -10420,10 +10420,10 @@
     </row>
     <row r="718" spans="1:4">
       <c r="A718">
-        <v>22.4</v>
+        <v>24.5</v>
       </c>
       <c r="B718">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C718" t="s">
         <v>5</v>
@@ -10434,10 +10434,10 @@
     </row>
     <row r="719" spans="1:4">
       <c r="A719">
-        <v>10</v>
+        <v>29.7</v>
       </c>
       <c r="B719">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C719" t="s">
         <v>5</v>
@@ -10448,10 +10448,10 @@
     </row>
     <row r="720" spans="1:4">
       <c r="A720">
-        <v>13.8</v>
+        <v>33.8</v>
       </c>
       <c r="B720">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C720" t="s">
         <v>5</v>
@@ -10462,10 +10462,10 @@
     </row>
     <row r="721" spans="1:4">
       <c r="A721">
-        <v>13.7</v>
+        <v>33.6</v>
       </c>
       <c r="B721">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C721" t="s">
         <v>5</v>
@@ -10476,10 +10476,10 @@
     </row>
     <row r="722" spans="1:4">
       <c r="A722">
-        <v>22.6</v>
+        <v>24.7</v>
       </c>
       <c r="B722">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C722" t="s">
         <v>5</v>
@@ -10490,10 +10490,10 @@
     </row>
     <row r="723" spans="1:4">
       <c r="A723">
-        <v>9.1</v>
+        <v>27</v>
       </c>
       <c r="B723">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C723" t="s">
         <v>5</v>
@@ -10504,10 +10504,10 @@
     </row>
     <row r="724" spans="1:4">
       <c r="A724">
-        <v>14.4</v>
+        <v>35.1</v>
       </c>
       <c r="B724">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C724" t="s">
         <v>5</v>
@@ -10518,10 +10518,10 @@
     </row>
     <row r="725" spans="1:4">
       <c r="A725">
-        <v>25.2</v>
+        <v>29.5</v>
       </c>
       <c r="B725">
-        <v>0.863</v>
+        <v>1.362</v>
       </c>
       <c r="C725" t="s">
         <v>5</v>
@@ -10532,10 +10532,10 @@
     </row>
     <row r="726" spans="1:4">
       <c r="A726">
-        <v>20.6</v>
+        <v>15.6</v>
       </c>
       <c r="B726">
-        <v>0.463</v>
+        <v>0.217</v>
       </c>
       <c r="C726" t="s">
         <v>5</v>
@@ -10546,10 +10546,10 @@
     </row>
     <row r="727" spans="1:4">
       <c r="A727">
-        <v>9.699999999999999</v>
+        <v>28.6</v>
       </c>
       <c r="B727">
-        <v>0.19</v>
+        <v>1.113</v>
       </c>
       <c r="C727" t="s">
         <v>5</v>
@@ -10560,10 +10560,10 @@
     </row>
     <row r="728" spans="1:4">
       <c r="A728">
-        <v>11.4</v>
+        <v>13.7</v>
       </c>
       <c r="B728">
-        <v>0.216</v>
+        <v>0.242</v>
       </c>
       <c r="C728" t="s">
         <v>5</v>
@@ -10574,10 +10574,10 @@
     </row>
     <row r="729" spans="1:4">
       <c r="A729">
-        <v>22.8</v>
+        <v>24.9</v>
       </c>
       <c r="B729">
-        <v>0.29</v>
+        <v>0.524</v>
       </c>
       <c r="C729" t="s">
         <v>5</v>
@@ -10588,10 +10588,10 @@
     </row>
     <row r="730" spans="1:4">
       <c r="A730">
-        <v>20.4</v>
+        <v>31.9</v>
       </c>
       <c r="B730">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C730" t="s">
         <v>5</v>
@@ -10602,10 +10602,10 @@
     </row>
     <row r="731" spans="1:4">
       <c r="A731">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="B731">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C731" t="s">
         <v>5</v>
@@ -10616,10 +10616,10 @@
     </row>
     <row r="732" spans="1:4">
       <c r="A732">
-        <v>18.6</v>
+        <v>29</v>
       </c>
       <c r="B732">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C732" t="s">
         <v>5</v>
@@ -10630,10 +10630,10 @@
     </row>
     <row r="733" spans="1:4">
       <c r="A733">
-        <v>10.7</v>
+        <v>7.9</v>
       </c>
       <c r="B733">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C733" t="s">
         <v>5</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="734" spans="1:4">
       <c r="A734">
-        <v>11</v>
+        <v>25.8</v>
       </c>
       <c r="B734">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C734" t="s">
         <v>5</v>
@@ -10658,10 +10658,10 @@
     </row>
     <row r="735" spans="1:4">
       <c r="A735">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="B735">
-        <v>0.209</v>
+        <v>0.208</v>
       </c>
       <c r="C735" t="s">
         <v>5</v>
@@ -10672,10 +10672,10 @@
     </row>
     <row r="736" spans="1:4">
       <c r="A736">
-        <v>11.6</v>
+        <v>27.2</v>
       </c>
       <c r="B736">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C736" t="s">
         <v>5</v>
@@ -10686,10 +10686,10 @@
     </row>
     <row r="737" spans="1:4">
       <c r="A737">
-        <v>11.1</v>
+        <v>26.2</v>
       </c>
       <c r="B737">
-        <v>0.118</v>
+        <v>0.695</v>
       </c>
       <c r="C737" t="s">
         <v>5</v>
@@ -10700,10 +10700,10 @@
     </row>
     <row r="738" spans="1:4">
       <c r="A738">
-        <v>23.8</v>
+        <v>27.8</v>
       </c>
       <c r="B738">
-        <v>0.863</v>
+        <v>1.362</v>
       </c>
       <c r="C738" t="s">
         <v>5</v>
@@ -10714,10 +10714,10 @@
     </row>
     <row r="739" spans="1:4">
       <c r="A739">
-        <v>1.1</v>
+        <v>19.7</v>
       </c>
       <c r="B739">
-        <v>0.274</v>
+        <v>0.422</v>
       </c>
       <c r="C739" t="s">
         <v>5</v>
@@ -10728,10 +10728,10 @@
     </row>
     <row r="740" spans="1:4">
       <c r="A740">
-        <v>20</v>
+        <v>31.3</v>
       </c>
       <c r="B740">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C740" t="s">
         <v>5</v>
@@ -10742,10 +10742,10 @@
     </row>
     <row r="741" spans="1:4">
       <c r="A741">
-        <v>10.6</v>
+        <v>21.1</v>
       </c>
       <c r="B741">
-        <v>0.161</v>
+        <v>0.263</v>
       </c>
       <c r="C741" t="s">
         <v>5</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="742" spans="1:4">
       <c r="A742">
-        <v>11.4</v>
+        <v>8.4</v>
       </c>
       <c r="B742">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C742" t="s">
         <v>5</v>
@@ -10770,10 +10770,10 @@
     </row>
     <row r="743" spans="1:4">
       <c r="A743">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="B743">
-        <v>1.153</v>
+        <v>0.668</v>
       </c>
       <c r="C743" t="s">
         <v>5</v>
@@ -10784,10 +10784,10 @@
     </row>
     <row r="744" spans="1:4">
       <c r="A744">
-        <v>10.2</v>
+        <v>7.5</v>
       </c>
       <c r="B744">
-        <v>0.245</v>
+        <v>0.316</v>
       </c>
       <c r="C744" t="s">
         <v>5</v>
@@ -10798,10 +10798,10 @@
     </row>
     <row r="745" spans="1:4">
       <c r="A745">
-        <v>25.9</v>
+        <v>11.9</v>
       </c>
       <c r="B745">
-        <v>0.28</v>
+        <v>0.19</v>
       </c>
       <c r="C745" t="s">
         <v>5</v>
@@ -10812,10 +10812,10 @@
     </row>
     <row r="746" spans="1:4">
       <c r="A746">
-        <v>13.6</v>
+        <v>33.4</v>
       </c>
       <c r="B746">
-        <v>0.237</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C746" t="s">
         <v>5</v>
@@ -10826,10 +10826,10 @@
     </row>
     <row r="747" spans="1:4">
       <c r="A747">
-        <v>20.5</v>
+        <v>32.1</v>
       </c>
       <c r="B747">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C747" t="s">
         <v>5</v>
@@ -10840,10 +10840,10 @@
     </row>
     <row r="748" spans="1:4">
       <c r="A748">
-        <v>16.7</v>
+        <v>11</v>
       </c>
       <c r="B748">
-        <v>0.154</v>
+        <v>0.1</v>
       </c>
       <c r="C748" t="s">
         <v>5</v>
@@ -10854,10 +10854,10 @@
     </row>
     <row r="749" spans="1:4">
       <c r="A749">
-        <v>19.6</v>
+        <v>30.7</v>
       </c>
       <c r="B749">
-        <v>0.279</v>
+        <v>0.746</v>
       </c>
       <c r="C749" t="s">
         <v>5</v>
@@ -10868,10 +10868,10 @@
     </row>
     <row r="750" spans="1:4">
       <c r="A750">
-        <v>35</v>
+        <v>29.8</v>
       </c>
       <c r="B750">
-        <v>1.541</v>
+        <v>1.74</v>
       </c>
       <c r="C750" t="s">
         <v>5</v>
@@ -10882,10 +10882,10 @@
     </row>
     <row r="751" spans="1:4">
       <c r="A751">
-        <v>26.9</v>
+        <v>26.6</v>
       </c>
       <c r="B751">
-        <v>1.153</v>
+        <v>0.668</v>
       </c>
       <c r="C751" t="s">
         <v>5</v>
